--- a/research/traditional_assets/database/data/oman/oman_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_hotel_gaming.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1031948963688802</v>
+        <v>0.1030783540243269</v>
       </c>
       <c r="C2">
-        <v>33.5</v>
+        <v>33.20893793121742</v>
       </c>
       <c r="D2">
-        <v>31.73</v>
+        <v>31.77393793121742</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="G2">
         <v>1.77</v>
@@ -1451,28 +1451,28 @@
         <v>2.47</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0168505</v>
       </c>
       <c r="N2">
-        <v>2.47</v>
+        <v>2.4531495</v>
       </c>
       <c r="O2">
-        <v>0.3704999999999999</v>
+        <v>0.367972425</v>
       </c>
       <c r="P2">
-        <v>2.0995</v>
+        <v>2.085177075</v>
       </c>
       <c r="Q2">
-        <v>3.2595</v>
+        <v>3.245177075</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1031948963688802</v>
+        <v>0.1036876808326534</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7544705382065601</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.5831874425091</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1030783540243269</v>
+        <v>0.1029618116797735</v>
       </c>
       <c r="C3">
-        <v>33.20893793121742</v>
+        <v>32.9179977167565</v>
       </c>
       <c r="D3">
-        <v>31.77393793121742</v>
+        <v>31.81799771675649</v>
       </c>
       <c r="E3">
-        <v>0.335</v>
+        <v>0.67</v>
       </c>
       <c r="F3">
-        <v>0.335</v>
+        <v>0.67</v>
       </c>
       <c r="G3">
         <v>1.77</v>
@@ -1533,28 +1533,28 @@
         <v>2.47</v>
       </c>
       <c r="M3">
-        <v>0.0168505</v>
+        <v>0.033701</v>
       </c>
       <c r="N3">
-        <v>2.4531495</v>
+        <v>2.436299</v>
       </c>
       <c r="O3">
-        <v>0.367972425</v>
+        <v>0.3654448499999999</v>
       </c>
       <c r="P3">
-        <v>2.085177075</v>
+        <v>2.07085415</v>
       </c>
       <c r="Q3">
-        <v>3.245177075</v>
+        <v>3.23085415</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1036876808326534</v>
+        <v>0.1041905221222179</v>
       </c>
       <c r="T3">
-        <v>0.7544705382065601</v>
+        <v>0.7610242458851759</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.5831874425091</v>
+        <v>73.29159372125454</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1029618116797735</v>
+        <v>0.1028452693352202</v>
       </c>
       <c r="C4">
-        <v>32.9179977167565</v>
+        <v>32.62717986423423</v>
       </c>
       <c r="D4">
-        <v>31.81799771675649</v>
+        <v>31.86217986423423</v>
       </c>
       <c r="E4">
-        <v>0.67</v>
+        <v>1.005</v>
       </c>
       <c r="F4">
-        <v>0.67</v>
+        <v>1.005</v>
       </c>
       <c r="G4">
         <v>1.77</v>
@@ -1615,28 +1615,28 @@
         <v>2.47</v>
       </c>
       <c r="M4">
-        <v>0.033701</v>
+        <v>0.05055149999999999</v>
       </c>
       <c r="N4">
-        <v>2.436299</v>
+        <v>2.4194485</v>
       </c>
       <c r="O4">
-        <v>0.3654448499999999</v>
+        <v>0.3629172749999999</v>
       </c>
       <c r="P4">
-        <v>2.07085415</v>
+        <v>2.056531225</v>
       </c>
       <c r="Q4">
-        <v>3.23085415</v>
+        <v>3.216531225</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1041905221222179</v>
+        <v>0.1047037312734229</v>
       </c>
       <c r="T4">
-        <v>0.7610242458851759</v>
+        <v>0.7677130815571649</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.29159372125454</v>
+        <v>48.86106248083637</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1028452693352202</v>
+        <v>0.1027287269906669</v>
       </c>
       <c r="C5">
-        <v>32.62717986423423</v>
+        <v>32.33648488409105</v>
       </c>
       <c r="D5">
-        <v>31.86217986423423</v>
+        <v>31.90648488409105</v>
       </c>
       <c r="E5">
-        <v>1.005</v>
+        <v>1.34</v>
       </c>
       <c r="F5">
-        <v>1.005</v>
+        <v>1.34</v>
       </c>
       <c r="G5">
         <v>1.77</v>
@@ -1697,28 +1697,28 @@
         <v>2.47</v>
       </c>
       <c r="M5">
-        <v>0.05055149999999999</v>
+        <v>0.067402</v>
       </c>
       <c r="N5">
-        <v>2.4194485</v>
+        <v>2.402598</v>
       </c>
       <c r="O5">
-        <v>0.3629172749999999</v>
+        <v>0.3603897</v>
       </c>
       <c r="P5">
-        <v>2.056531225</v>
+        <v>2.0422083</v>
       </c>
       <c r="Q5">
-        <v>3.216531225</v>
+        <v>3.2022083</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1047037312734229</v>
+        <v>0.1052276322819447</v>
       </c>
       <c r="T5">
-        <v>0.7677130815571649</v>
+        <v>0.7745412679723206</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.86106248083637</v>
+        <v>36.64579686062728</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1027287269906669</v>
+        <v>0.1026121846461136</v>
       </c>
       <c r="C6">
-        <v>32.33648488409105</v>
+        <v>32.04591328961044</v>
       </c>
       <c r="D6">
-        <v>31.90648488409105</v>
+        <v>31.95091328961044</v>
       </c>
       <c r="E6">
-        <v>1.34</v>
+        <v>1.675</v>
       </c>
       <c r="F6">
-        <v>1.34</v>
+        <v>1.675</v>
       </c>
       <c r="G6">
         <v>1.77</v>
@@ -1779,28 +1779,28 @@
         <v>2.47</v>
       </c>
       <c r="M6">
-        <v>0.067402</v>
+        <v>0.08425249999999999</v>
       </c>
       <c r="N6">
-        <v>2.402598</v>
+        <v>2.3857475</v>
       </c>
       <c r="O6">
-        <v>0.3603897</v>
+        <v>0.357862125</v>
       </c>
       <c r="P6">
-        <v>2.0422083</v>
+        <v>2.027885375</v>
       </c>
       <c r="Q6">
-        <v>3.2022083</v>
+        <v>3.187885375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1052276322819447</v>
+        <v>0.1057625627853827</v>
       </c>
       <c r="T6">
-        <v>0.7745412679723206</v>
+        <v>0.7815132056804268</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.64579686062728</v>
+        <v>29.31663748850183</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1026121846461136</v>
+        <v>0.1024956423015603</v>
       </c>
       <c r="C7">
-        <v>32.04591328961044</v>
+        <v>31.75546559693874</v>
       </c>
       <c r="D7">
-        <v>31.95091328961044</v>
+        <v>31.99546559693874</v>
       </c>
       <c r="E7">
-        <v>1.675</v>
+        <v>2.01</v>
       </c>
       <c r="F7">
-        <v>1.675</v>
+        <v>2.01</v>
       </c>
       <c r="G7">
         <v>1.77</v>
@@ -1861,28 +1861,28 @@
         <v>2.47</v>
       </c>
       <c r="M7">
-        <v>0.08425249999999999</v>
+        <v>0.101103</v>
       </c>
       <c r="N7">
-        <v>2.3857475</v>
+        <v>2.368897</v>
       </c>
       <c r="O7">
-        <v>0.357862125</v>
+        <v>0.3553345499999999</v>
       </c>
       <c r="P7">
-        <v>2.027885375</v>
+        <v>2.01356245</v>
       </c>
       <c r="Q7">
-        <v>3.187885375</v>
+        <v>3.173562449999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1057625627853827</v>
+        <v>0.1063088747888939</v>
       </c>
       <c r="T7">
-        <v>0.7815132056804268</v>
+        <v>0.7886334824887055</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.31663748850183</v>
+        <v>24.43053124041818</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1024956423015602</v>
+        <v>0.1023790999570069</v>
       </c>
       <c r="C8">
-        <v>31.75546559693876</v>
+        <v>31.46514232510523</v>
       </c>
       <c r="D8">
-        <v>31.99546559693875</v>
+        <v>32.04014232510523</v>
       </c>
       <c r="E8">
-        <v>2.01</v>
+        <v>2.345</v>
       </c>
       <c r="F8">
-        <v>2.01</v>
+        <v>2.345</v>
       </c>
       <c r="G8">
         <v>1.77</v>
@@ -1943,28 +1943,28 @@
         <v>2.47</v>
       </c>
       <c r="M8">
-        <v>0.101103</v>
+        <v>0.1179535</v>
       </c>
       <c r="N8">
-        <v>2.368897</v>
+        <v>2.3520465</v>
       </c>
       <c r="O8">
-        <v>0.3553345499999999</v>
+        <v>0.352806975</v>
       </c>
       <c r="P8">
-        <v>2.01356245</v>
+        <v>1.999239525</v>
       </c>
       <c r="Q8">
-        <v>3.173562449999999</v>
+        <v>3.159239524999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1063088747888939</v>
+        <v>0.1068669354376419</v>
       </c>
       <c r="T8">
-        <v>0.7886334824887055</v>
+        <v>0.7959068835294203</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.43053124041819</v>
+        <v>20.94045534892988</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1023790999570069</v>
+        <v>0.1022625576124536</v>
       </c>
       <c r="C9">
-        <v>31.46514232510524</v>
+        <v>31.17494399604217</v>
       </c>
       <c r="D9">
-        <v>32.04014232510524</v>
+        <v>32.08494399604216</v>
       </c>
       <c r="E9">
-        <v>2.345</v>
+        <v>2.68</v>
       </c>
       <c r="F9">
-        <v>2.345</v>
+        <v>2.68</v>
       </c>
       <c r="G9">
         <v>1.77</v>
@@ -2025,28 +2025,28 @@
         <v>2.47</v>
       </c>
       <c r="M9">
-        <v>0.1179535</v>
+        <v>0.134804</v>
       </c>
       <c r="N9">
-        <v>2.3520465</v>
+        <v>2.335196</v>
       </c>
       <c r="O9">
-        <v>0.352806975</v>
+        <v>0.3502794</v>
       </c>
       <c r="P9">
-        <v>1.999239525</v>
+        <v>1.9849166</v>
       </c>
       <c r="Q9">
-        <v>3.159239524999999</v>
+        <v>3.1449166</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1068669354376419</v>
+        <v>0.1074371278396235</v>
       </c>
       <c r="T9">
-        <v>0.7959068835294203</v>
+        <v>0.8033384019840637</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.94045534892987</v>
+        <v>18.32289843031364</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1022625576124536</v>
+        <v>0.1021460152679003</v>
       </c>
       <c r="C10">
-        <v>31.17494399604217</v>
+        <v>30.88487113460519</v>
       </c>
       <c r="D10">
-        <v>32.08494399604216</v>
+        <v>32.12987113460519</v>
       </c>
       <c r="E10">
-        <v>2.68</v>
+        <v>3.015</v>
       </c>
       <c r="F10">
-        <v>2.68</v>
+        <v>3.015</v>
       </c>
       <c r="G10">
         <v>1.77</v>
@@ -2107,28 +2107,28 @@
         <v>2.47</v>
       </c>
       <c r="M10">
-        <v>0.134804</v>
+        <v>0.1516545</v>
       </c>
       <c r="N10">
-        <v>2.335196</v>
+        <v>2.3183455</v>
       </c>
       <c r="O10">
-        <v>0.3502794</v>
+        <v>0.347751825</v>
       </c>
       <c r="P10">
-        <v>1.9849166</v>
+        <v>1.970593675</v>
       </c>
       <c r="Q10">
-        <v>3.1449166</v>
+        <v>3.130593675</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1074371278396235</v>
+        <v>0.1080198519427476</v>
       </c>
       <c r="T10">
-        <v>0.8033384019840637</v>
+        <v>0.8109332505146333</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.32289843031364</v>
+        <v>16.28702082694546</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1021460152679003</v>
+        <v>0.102029472923347</v>
       </c>
       <c r="C11">
-        <v>30.88487113460519</v>
+        <v>30.59492426859378</v>
       </c>
       <c r="D11">
-        <v>32.12987113460519</v>
+        <v>32.17492426859378</v>
       </c>
       <c r="E11">
-        <v>3.015</v>
+        <v>3.35</v>
       </c>
       <c r="F11">
-        <v>3.015</v>
+        <v>3.35</v>
       </c>
       <c r="G11">
         <v>1.77</v>
@@ -2189,28 +2189,28 @@
         <v>2.47</v>
       </c>
       <c r="M11">
-        <v>0.1516545</v>
+        <v>0.168505</v>
       </c>
       <c r="N11">
-        <v>2.3183455</v>
+        <v>2.301495</v>
       </c>
       <c r="O11">
-        <v>0.347751825</v>
+        <v>0.34522425</v>
       </c>
       <c r="P11">
-        <v>1.970593675</v>
+        <v>1.95627075</v>
       </c>
       <c r="Q11">
-        <v>3.130593675</v>
+        <v>3.11627075</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1080198519427476</v>
+        <v>0.1086155254703855</v>
       </c>
       <c r="T11">
-        <v>0.8109332505146333</v>
+        <v>0.8186968734569935</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.28702082694546</v>
+        <v>14.65831874425091</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.102029472923347</v>
+        <v>0.1019129305787937</v>
       </c>
       <c r="C12">
-        <v>30.59492426859378</v>
+        <v>30.30510392877192</v>
       </c>
       <c r="D12">
-        <v>32.17492426859378</v>
+        <v>32.22010392877191</v>
       </c>
       <c r="E12">
-        <v>3.35</v>
+        <v>3.685</v>
       </c>
       <c r="F12">
-        <v>3.35</v>
+        <v>3.685</v>
       </c>
       <c r="G12">
         <v>1.77</v>
@@ -2271,28 +2271,28 @@
         <v>2.47</v>
       </c>
       <c r="M12">
-        <v>0.168505</v>
+        <v>0.1853555</v>
       </c>
       <c r="N12">
-        <v>2.301495</v>
+        <v>2.2846445</v>
       </c>
       <c r="O12">
-        <v>0.34522425</v>
+        <v>0.342696675</v>
       </c>
       <c r="P12">
-        <v>1.95627075</v>
+        <v>1.941947825</v>
       </c>
       <c r="Q12">
-        <v>3.11627075</v>
+        <v>3.101947825</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1086155254703855</v>
+        <v>0.1092245849199929</v>
       </c>
       <c r="T12">
-        <v>0.8186968734569935</v>
+        <v>0.8266349598362605</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.65831874425091</v>
+        <v>13.32574431295537</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1019129305787937</v>
+        <v>0.1019493882342404</v>
       </c>
       <c r="C13">
-        <v>30.30510392877192</v>
+        <v>29.95595685498006</v>
       </c>
       <c r="D13">
-        <v>32.22010392877191</v>
+        <v>32.20595685498006</v>
       </c>
       <c r="E13">
-        <v>3.685</v>
+        <v>4.02</v>
       </c>
       <c r="F13">
-        <v>3.685</v>
+        <v>4.02</v>
       </c>
       <c r="G13">
         <v>1.77</v>
@@ -2353,45 +2353,45 @@
         <v>2.47</v>
       </c>
       <c r="M13">
-        <v>0.1853555</v>
+        <v>0.208236</v>
       </c>
       <c r="N13">
-        <v>2.2846445</v>
+        <v>2.261764</v>
       </c>
       <c r="O13">
-        <v>0.342696675</v>
+        <v>0.3392646</v>
       </c>
       <c r="P13">
-        <v>1.941947825</v>
+        <v>1.9224994</v>
       </c>
       <c r="Q13">
-        <v>3.101947825</v>
+        <v>3.0824994</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1092245849199929</v>
+        <v>0.1098474866298186</v>
       </c>
       <c r="T13">
-        <v>0.8266349598362605</v>
+        <v>0.8347534572696018</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.32574431295537</v>
+        <v>11.86154171228798</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1019493882342404</v>
+        <v>0.101845595889687</v>
       </c>
       <c r="C14">
-        <v>29.95595685498006</v>
+        <v>29.66126526710683</v>
       </c>
       <c r="D14">
-        <v>32.20595685498006</v>
+        <v>32.24626526710683</v>
       </c>
       <c r="E14">
-        <v>4.02</v>
+        <v>4.355</v>
       </c>
       <c r="F14">
-        <v>4.02</v>
+        <v>4.355</v>
       </c>
       <c r="G14">
         <v>1.77</v>
@@ -2435,28 +2435,28 @@
         <v>2.47</v>
       </c>
       <c r="M14">
-        <v>0.208236</v>
+        <v>0.225589</v>
       </c>
       <c r="N14">
-        <v>2.261764</v>
+        <v>2.244411</v>
       </c>
       <c r="O14">
-        <v>0.3392646</v>
+        <v>0.33666165</v>
       </c>
       <c r="P14">
-        <v>1.9224994</v>
+        <v>1.90774935</v>
       </c>
       <c r="Q14">
-        <v>3.0824994</v>
+        <v>3.06774935</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1098474866298186</v>
+        <v>0.1104847079191805</v>
       </c>
       <c r="T14">
-        <v>0.8347534572696018</v>
+        <v>0.8430585868278474</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.86154171228798</v>
+        <v>10.94911542672737</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.101845595889687</v>
+        <v>0.1017418035451337</v>
       </c>
       <c r="C15">
-        <v>29.66126526710683</v>
+        <v>29.36667470428154</v>
       </c>
       <c r="D15">
-        <v>32.24626526710683</v>
+        <v>32.28667470428154</v>
       </c>
       <c r="E15">
-        <v>4.355</v>
+        <v>4.69</v>
       </c>
       <c r="F15">
-        <v>4.355</v>
+        <v>4.69</v>
       </c>
       <c r="G15">
         <v>1.77</v>
@@ -2517,28 +2517,28 @@
         <v>2.47</v>
       </c>
       <c r="M15">
-        <v>0.225589</v>
+        <v>0.242942</v>
       </c>
       <c r="N15">
-        <v>2.244411</v>
+        <v>2.227058</v>
       </c>
       <c r="O15">
-        <v>0.33666165</v>
+        <v>0.3340586999999999</v>
       </c>
       <c r="P15">
-        <v>1.90774935</v>
+        <v>1.8929993</v>
       </c>
       <c r="Q15">
-        <v>3.06774935</v>
+        <v>3.0529993</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1104847079191805</v>
+        <v>0.111136748308295</v>
       </c>
       <c r="T15">
-        <v>0.8430585868278474</v>
+        <v>0.8515568589339592</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.94911542672737</v>
+        <v>10.1670357533897</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1017418035451337</v>
+        <v>0.1018547612005804</v>
       </c>
       <c r="C16">
-        <v>29.36667470428154</v>
+        <v>28.98770179971569</v>
       </c>
       <c r="D16">
-        <v>32.28667470428154</v>
+        <v>32.24270179971568</v>
       </c>
       <c r="E16">
-        <v>4.69</v>
+        <v>5.025</v>
       </c>
       <c r="F16">
-        <v>4.69</v>
+        <v>5.025</v>
       </c>
       <c r="G16">
         <v>1.77</v>
@@ -2599,45 +2599,45 @@
         <v>2.47</v>
       </c>
       <c r="M16">
-        <v>0.242942</v>
+        <v>0.2688375</v>
       </c>
       <c r="N16">
-        <v>2.227058</v>
+        <v>2.2011625</v>
       </c>
       <c r="O16">
-        <v>0.3340586999999999</v>
+        <v>0.330174375</v>
       </c>
       <c r="P16">
-        <v>1.8929993</v>
+        <v>1.870988125</v>
       </c>
       <c r="Q16">
-        <v>3.0529993</v>
+        <v>3.030988124999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.111136748308295</v>
+        <v>0.1118041308242122</v>
       </c>
       <c r="T16">
-        <v>0.8515568589339592</v>
+        <v>0.8602550903837443</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.1670357533897</v>
+        <v>9.187706328172222</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1018547612005804</v>
+        <v>0.1017654188560271</v>
       </c>
       <c r="C17">
-        <v>28.98770179971569</v>
+        <v>28.68747166590621</v>
       </c>
       <c r="D17">
-        <v>32.24270179971568</v>
+        <v>32.27747166590621</v>
       </c>
       <c r="E17">
-        <v>5.024999999999999</v>
+        <v>5.36</v>
       </c>
       <c r="F17">
-        <v>5.024999999999999</v>
+        <v>5.36</v>
       </c>
       <c r="G17">
         <v>1.77</v>
@@ -2681,28 +2681,28 @@
         <v>2.47</v>
       </c>
       <c r="M17">
-        <v>0.2688375</v>
+        <v>0.28676</v>
       </c>
       <c r="N17">
-        <v>2.2011625</v>
+        <v>2.18324</v>
       </c>
       <c r="O17">
-        <v>0.330174375</v>
+        <v>0.3274859999999999</v>
       </c>
       <c r="P17">
-        <v>1.870988125</v>
+        <v>1.855754</v>
       </c>
       <c r="Q17">
-        <v>3.030988124999999</v>
+        <v>3.015753999999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1118041308242122</v>
+        <v>0.1124874034000322</v>
       </c>
       <c r="T17">
-        <v>0.8602550903837443</v>
+        <v>0.8691604225823339</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.187706328172224</v>
+        <v>8.613474682661458</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1017654188560271</v>
+        <v>0.1016760765114737</v>
       </c>
       <c r="C18">
-        <v>28.68747166590621</v>
+        <v>28.38731660326849</v>
       </c>
       <c r="D18">
-        <v>32.27747166590621</v>
+        <v>32.31231660326849</v>
       </c>
       <c r="E18">
-        <v>5.36</v>
+        <v>5.695</v>
       </c>
       <c r="F18">
-        <v>5.36</v>
+        <v>5.695</v>
       </c>
       <c r="G18">
         <v>1.77</v>
@@ -2763,28 +2763,28 @@
         <v>2.47</v>
       </c>
       <c r="M18">
-        <v>0.28676</v>
+        <v>0.3046825</v>
       </c>
       <c r="N18">
-        <v>2.18324</v>
+        <v>2.1653175</v>
       </c>
       <c r="O18">
-        <v>0.3274859999999999</v>
+        <v>0.3247976249999999</v>
       </c>
       <c r="P18">
-        <v>1.855754</v>
+        <v>1.840519875</v>
       </c>
       <c r="Q18">
-        <v>3.015753999999999</v>
+        <v>3.000519874999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1124874034000322</v>
+        <v>0.1131871403752696</v>
       </c>
       <c r="T18">
-        <v>0.8691604225823339</v>
+        <v>0.8782803410989616</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.613474682661458</v>
+        <v>8.106799701328431</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1016760765114737</v>
+        <v>0.1015867341669204</v>
       </c>
       <c r="C19">
-        <v>28.38731660326849</v>
+        <v>28.08723685519308</v>
       </c>
       <c r="D19">
-        <v>32.31231660326849</v>
+        <v>32.34723685519307</v>
       </c>
       <c r="E19">
-        <v>5.695</v>
+        <v>6.030000000000001</v>
       </c>
       <c r="F19">
-        <v>5.695</v>
+        <v>6.030000000000001</v>
       </c>
       <c r="G19">
         <v>1.77</v>
@@ -2845,28 +2845,28 @@
         <v>2.47</v>
       </c>
       <c r="M19">
-        <v>0.3046825</v>
+        <v>0.322605</v>
       </c>
       <c r="N19">
-        <v>2.1653175</v>
+        <v>2.147394999999999</v>
       </c>
       <c r="O19">
-        <v>0.3247976249999999</v>
+        <v>0.3221092499999999</v>
       </c>
       <c r="P19">
-        <v>1.840519875</v>
+        <v>1.825285749999999</v>
       </c>
       <c r="Q19">
-        <v>3.000519874999999</v>
+        <v>2.985285749999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1131871403752696</v>
+        <v>0.1139039441060005</v>
       </c>
       <c r="T19">
-        <v>0.8782803410989616</v>
+        <v>0.8876226966525803</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.106799701328431</v>
+        <v>7.656421940143517</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1015867341669204</v>
+        <v>0.1016265918223671</v>
       </c>
       <c r="C20">
-        <v>28.08723685519307</v>
+        <v>27.73664881457125</v>
       </c>
       <c r="D20">
-        <v>32.34723685519307</v>
+        <v>32.33164881457125</v>
       </c>
       <c r="E20">
-        <v>6.029999999999999</v>
+        <v>6.365</v>
       </c>
       <c r="F20">
-        <v>6.029999999999999</v>
+        <v>6.365</v>
       </c>
       <c r="G20">
         <v>1.77</v>
@@ -2927,45 +2927,45 @@
         <v>2.47</v>
       </c>
       <c r="M20">
-        <v>0.322605</v>
+        <v>0.3456195</v>
       </c>
       <c r="N20">
-        <v>2.147395</v>
+        <v>2.1243805</v>
       </c>
       <c r="O20">
-        <v>0.32210925</v>
+        <v>0.3186570749999999</v>
       </c>
       <c r="P20">
-        <v>1.82528575</v>
+        <v>1.805723425</v>
       </c>
       <c r="Q20">
-        <v>2.98528575</v>
+        <v>2.965723424999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1139039441060005</v>
+        <v>0.1146384466942804</v>
       </c>
       <c r="T20">
-        <v>0.8876226966525803</v>
+        <v>0.8971957276519673</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.656421940143519</v>
+        <v>7.146587504466615</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1016265918223671</v>
+        <v>0.1015440494778138</v>
       </c>
       <c r="C21">
-        <v>27.73664881457125</v>
+        <v>27.43394720472264</v>
       </c>
       <c r="D21">
-        <v>32.33164881457125</v>
+        <v>32.36394720472263</v>
       </c>
       <c r="E21">
-        <v>6.365</v>
+        <v>6.7</v>
       </c>
       <c r="F21">
-        <v>6.365</v>
+        <v>6.7</v>
       </c>
       <c r="G21">
         <v>1.77</v>
@@ -3009,28 +3009,28 @@
         <v>2.47</v>
       </c>
       <c r="M21">
-        <v>0.3456195</v>
+        <v>0.36381</v>
       </c>
       <c r="N21">
-        <v>2.1243805</v>
+        <v>2.10619</v>
       </c>
       <c r="O21">
-        <v>0.3186570749999999</v>
+        <v>0.3159284999999999</v>
       </c>
       <c r="P21">
-        <v>1.805723425</v>
+        <v>1.7902615</v>
       </c>
       <c r="Q21">
-        <v>2.965723424999999</v>
+        <v>2.9502615</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1146384466942804</v>
+        <v>0.1153913118472672</v>
       </c>
       <c r="T21">
-        <v>0.8971957276519673</v>
+        <v>0.9070080844263391</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.146587504466615</v>
+        <v>6.789258129243286</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1015440494778138</v>
+        <v>0.1014615071332605</v>
       </c>
       <c r="C22">
-        <v>27.43394720472264</v>
+        <v>27.13131018973384</v>
       </c>
       <c r="D22">
-        <v>32.36394720472263</v>
+        <v>32.39631018973384</v>
       </c>
       <c r="E22">
-        <v>6.7</v>
+        <v>7.035000000000001</v>
       </c>
       <c r="F22">
-        <v>6.7</v>
+        <v>7.035000000000001</v>
       </c>
       <c r="G22">
         <v>1.77</v>
@@ -3091,28 +3091,28 @@
         <v>2.47</v>
       </c>
       <c r="M22">
-        <v>0.36381</v>
+        <v>0.3820005000000001</v>
       </c>
       <c r="N22">
-        <v>2.10619</v>
+        <v>2.0879995</v>
       </c>
       <c r="O22">
-        <v>0.3159284999999999</v>
+        <v>0.3131999249999999</v>
       </c>
       <c r="P22">
-        <v>1.7902615</v>
+        <v>1.774799575</v>
       </c>
       <c r="Q22">
-        <v>2.9502615</v>
+        <v>2.934799575</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1153913118472672</v>
+        <v>0.1161632368775449</v>
       </c>
       <c r="T22">
-        <v>0.9070080844263391</v>
+        <v>0.9170688552962647</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.789258129243286</v>
+        <v>6.465960123088842</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1014615071332605</v>
+        <v>0.1013789647887072</v>
       </c>
       <c r="C23">
-        <v>27.13131018973384</v>
+        <v>26.82873796357764</v>
       </c>
       <c r="D23">
-        <v>32.39631018973384</v>
+        <v>32.42873796357764</v>
       </c>
       <c r="E23">
-        <v>7.035</v>
+        <v>7.37</v>
       </c>
       <c r="F23">
-        <v>7.035</v>
+        <v>7.37</v>
       </c>
       <c r="G23">
         <v>1.77</v>
@@ -3173,28 +3173,28 @@
         <v>2.47</v>
       </c>
       <c r="M23">
-        <v>0.3820005</v>
+        <v>0.400191</v>
       </c>
       <c r="N23">
-        <v>2.0879995</v>
+        <v>2.069809</v>
       </c>
       <c r="O23">
-        <v>0.3131999249999999</v>
+        <v>0.31047135</v>
       </c>
       <c r="P23">
-        <v>1.774799575</v>
+        <v>1.75933765</v>
       </c>
       <c r="Q23">
-        <v>2.934799575</v>
+        <v>2.91933765</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1161632368775449</v>
+        <v>0.1169549548573169</v>
       </c>
       <c r="T23">
-        <v>0.9170688552962645</v>
+        <v>0.9273875946500344</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.465960123088843</v>
+        <v>6.172052844766623</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1013789647887072</v>
+        <v>0.1014919224441538</v>
       </c>
       <c r="C24">
-        <v>26.82873796357764</v>
+        <v>26.44937750680126</v>
       </c>
       <c r="D24">
-        <v>32.42873796357764</v>
+        <v>32.38437750680125</v>
       </c>
       <c r="E24">
-        <v>7.37</v>
+        <v>7.705</v>
       </c>
       <c r="F24">
-        <v>7.37</v>
+        <v>7.705</v>
       </c>
       <c r="G24">
         <v>1.77</v>
@@ -3255,45 +3255,45 @@
         <v>2.47</v>
       </c>
       <c r="M24">
-        <v>0.400191</v>
+        <v>0.4260865</v>
       </c>
       <c r="N24">
-        <v>2.069809</v>
+        <v>2.043913499999999</v>
       </c>
       <c r="O24">
-        <v>0.31047135</v>
+        <v>0.3065870249999999</v>
       </c>
       <c r="P24">
-        <v>1.75933765</v>
+        <v>1.737326475</v>
       </c>
       <c r="Q24">
-        <v>2.91933765</v>
+        <v>2.897326475</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1169549548573169</v>
+        <v>0.1177672369404595</v>
       </c>
       <c r="T24">
-        <v>0.9273875946500344</v>
+        <v>0.937974353207798</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.172052844766623</v>
+        <v>5.796944986522688</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1014919224441538</v>
+        <v>0.1014178800996005</v>
       </c>
       <c r="C25">
-        <v>26.44937750680126</v>
+        <v>26.14344152117452</v>
       </c>
       <c r="D25">
-        <v>32.38437750680125</v>
+        <v>32.41344152117452</v>
       </c>
       <c r="E25">
-        <v>7.705</v>
+        <v>8.040000000000001</v>
       </c>
       <c r="F25">
-        <v>7.705</v>
+        <v>8.040000000000001</v>
       </c>
       <c r="G25">
         <v>1.77</v>
@@ -3337,28 +3337,28 @@
         <v>2.47</v>
       </c>
       <c r="M25">
-        <v>0.4260865</v>
+        <v>0.4446120000000001</v>
       </c>
       <c r="N25">
-        <v>2.043913499999999</v>
+        <v>2.025388</v>
       </c>
       <c r="O25">
-        <v>0.3065870249999999</v>
+        <v>0.3038081999999999</v>
       </c>
       <c r="P25">
-        <v>1.737326475</v>
+        <v>1.7215798</v>
       </c>
       <c r="Q25">
-        <v>2.897326475</v>
+        <v>2.881579799999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1177672369404595</v>
+        <v>0.1186008948678954</v>
       </c>
       <c r="T25">
-        <v>0.937974353207798</v>
+        <v>0.9488397106749765</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.796944986522688</v>
+        <v>5.555405612084242</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1014178800996005</v>
+        <v>0.1013438377550472</v>
       </c>
       <c r="C26">
-        <v>26.14344152117452</v>
+        <v>25.83755775058393</v>
       </c>
       <c r="D26">
-        <v>32.41344152117452</v>
+        <v>32.44255775058393</v>
       </c>
       <c r="E26">
-        <v>8.039999999999999</v>
+        <v>8.375</v>
       </c>
       <c r="F26">
-        <v>8.039999999999999</v>
+        <v>8.375</v>
       </c>
       <c r="G26">
         <v>1.77</v>
@@ -3419,28 +3419,28 @@
         <v>2.47</v>
       </c>
       <c r="M26">
-        <v>0.444612</v>
+        <v>0.4631375</v>
       </c>
       <c r="N26">
-        <v>2.025388</v>
+        <v>2.0068625</v>
       </c>
       <c r="O26">
-        <v>0.3038082</v>
+        <v>0.3010293749999999</v>
       </c>
       <c r="P26">
-        <v>1.7215798</v>
+        <v>1.705833125</v>
       </c>
       <c r="Q26">
-        <v>2.8815798</v>
+        <v>2.865833125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1186008948678954</v>
+        <v>0.1194567836733962</v>
       </c>
       <c r="T26">
-        <v>0.9488397106749765</v>
+        <v>0.9599948110079465</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.555405612084245</v>
+        <v>5.333189387600873</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1013438377550472</v>
+        <v>0.1012697954104938</v>
       </c>
       <c r="C27">
-        <v>25.83755775058393</v>
+        <v>25.53172633586658</v>
       </c>
       <c r="D27">
-        <v>32.44255775058393</v>
+        <v>32.47172633586658</v>
       </c>
       <c r="E27">
-        <v>8.375</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F27">
-        <v>8.375</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G27">
         <v>1.77</v>
@@ -3501,28 +3501,28 @@
         <v>2.47</v>
       </c>
       <c r="M27">
-        <v>0.4631375</v>
+        <v>0.4816630000000001</v>
       </c>
       <c r="N27">
-        <v>2.0068625</v>
+        <v>1.988337</v>
       </c>
       <c r="O27">
-        <v>0.3010293749999999</v>
+        <v>0.2982505499999999</v>
       </c>
       <c r="P27">
-        <v>1.705833125</v>
+        <v>1.69008645</v>
       </c>
       <c r="Q27">
-        <v>2.865833125</v>
+        <v>2.85008645</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1194567836733962</v>
+        <v>0.1203358046087755</v>
       </c>
       <c r="T27">
-        <v>0.9599948110079465</v>
+        <v>0.9714514005391049</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.333189387600873</v>
+        <v>5.128066718846993</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1012697954104938</v>
+        <v>0.1011957530659405</v>
       </c>
       <c r="C28">
-        <v>25.53172633586658</v>
+        <v>25.22594741836654</v>
       </c>
       <c r="D28">
-        <v>32.47172633586658</v>
+        <v>32.50094741836654</v>
       </c>
       <c r="E28">
-        <v>8.710000000000001</v>
+        <v>9.045</v>
       </c>
       <c r="F28">
-        <v>8.710000000000001</v>
+        <v>9.045</v>
       </c>
       <c r="G28">
         <v>1.77</v>
@@ -3583,28 +3583,28 @@
         <v>2.47</v>
       </c>
       <c r="M28">
-        <v>0.4816630000000001</v>
+        <v>0.5001885</v>
       </c>
       <c r="N28">
-        <v>1.988337</v>
+        <v>1.9698115</v>
       </c>
       <c r="O28">
-        <v>0.2982505499999999</v>
+        <v>0.2954717249999999</v>
       </c>
       <c r="P28">
-        <v>1.69008645</v>
+        <v>1.674339775</v>
       </c>
       <c r="Q28">
-        <v>2.85008645</v>
+        <v>2.834339775</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1203358046087755</v>
+        <v>0.1212389083095076</v>
       </c>
       <c r="T28">
-        <v>0.9714514005391049</v>
+        <v>0.9832218692355006</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.128066718846993</v>
+        <v>4.93813832185266</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1011957530659405</v>
+        <v>0.1011217107213872</v>
       </c>
       <c r="C29">
-        <v>25.22594741836654</v>
+        <v>24.92022113993711</v>
       </c>
       <c r="D29">
-        <v>32.50094741836654</v>
+        <v>32.53022113993711</v>
       </c>
       <c r="E29">
-        <v>9.045</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F29">
-        <v>9.045</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G29">
         <v>1.77</v>
@@ -3665,28 +3665,28 @@
         <v>2.47</v>
       </c>
       <c r="M29">
-        <v>0.5001885</v>
+        <v>0.518714</v>
       </c>
       <c r="N29">
-        <v>1.9698115</v>
+        <v>1.951286</v>
       </c>
       <c r="O29">
-        <v>0.2954717249999999</v>
+        <v>0.2926928999999999</v>
       </c>
       <c r="P29">
-        <v>1.674339775</v>
+        <v>1.6585931</v>
       </c>
       <c r="Q29">
-        <v>2.834339775</v>
+        <v>2.818593099999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1212389083095076</v>
+        <v>0.1221670982241489</v>
       </c>
       <c r="T29">
-        <v>0.9832218692355006</v>
+        <v>0.995319295395685</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.93813832185266</v>
+        <v>4.761776238929352</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1011217107213872</v>
+        <v>0.1010476683768339</v>
       </c>
       <c r="C30">
-        <v>24.92022113993711</v>
+        <v>24.61454764294314</v>
       </c>
       <c r="D30">
-        <v>32.53022113993711</v>
+        <v>32.55954764294314</v>
       </c>
       <c r="E30">
-        <v>9.380000000000001</v>
+        <v>9.715000000000002</v>
       </c>
       <c r="F30">
-        <v>9.380000000000001</v>
+        <v>9.715000000000002</v>
       </c>
       <c r="G30">
         <v>1.77</v>
@@ -3747,28 +3747,28 @@
         <v>2.47</v>
       </c>
       <c r="M30">
-        <v>0.518714</v>
+        <v>0.5372395000000001</v>
       </c>
       <c r="N30">
-        <v>1.951286</v>
+        <v>1.9327605</v>
       </c>
       <c r="O30">
-        <v>0.2926928999999999</v>
+        <v>0.2899140749999999</v>
       </c>
       <c r="P30">
-        <v>1.6585931</v>
+        <v>1.642846425</v>
       </c>
       <c r="Q30">
-        <v>2.818593099999999</v>
+        <v>2.802846424999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1221670982241489</v>
+        <v>0.1231214343335689</v>
       </c>
       <c r="T30">
-        <v>0.995319295395685</v>
+        <v>1.007757494123762</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.761776238929352</v>
+        <v>4.597577058276615</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1010476683768339</v>
+        <v>0.1016111260322806</v>
       </c>
       <c r="C31">
-        <v>24.61454764294314</v>
+        <v>24.0576955890522</v>
       </c>
       <c r="D31">
-        <v>32.55954764294314</v>
+        <v>32.3376955890522</v>
       </c>
       <c r="E31">
-        <v>9.715</v>
+        <v>10.05</v>
       </c>
       <c r="F31">
-        <v>9.715</v>
+        <v>10.05</v>
       </c>
       <c r="G31">
         <v>1.77</v>
@@ -3829,45 +3829,45 @@
         <v>2.47</v>
       </c>
       <c r="M31">
-        <v>0.5372395</v>
+        <v>0.58089</v>
       </c>
       <c r="N31">
-        <v>1.9327605</v>
+        <v>1.88911</v>
       </c>
       <c r="O31">
-        <v>0.2899140749999999</v>
+        <v>0.2833664999999999</v>
       </c>
       <c r="P31">
-        <v>1.642846425</v>
+        <v>1.6057435</v>
       </c>
       <c r="Q31">
-        <v>2.802846424999999</v>
+        <v>2.7657435</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1231214343335689</v>
+        <v>0.1241030371889723</v>
       </c>
       <c r="T31">
-        <v>1.007757494123762</v>
+        <v>1.020551069958355</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.597577058276615</v>
+        <v>4.252095921775206</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1016111260322806</v>
+        <v>0.1015583336877273</v>
       </c>
       <c r="C32">
-        <v>24.0576955890522</v>
+        <v>23.74335325113825</v>
       </c>
       <c r="D32">
-        <v>32.3376955890522</v>
+        <v>32.35835325113824</v>
       </c>
       <c r="E32">
-        <v>10.05</v>
+        <v>10.385</v>
       </c>
       <c r="F32">
-        <v>10.05</v>
+        <v>10.385</v>
       </c>
       <c r="G32">
         <v>1.77</v>
@@ -3911,28 +3911,28 @@
         <v>2.47</v>
       </c>
       <c r="M32">
-        <v>0.58089</v>
+        <v>0.600253</v>
       </c>
       <c r="N32">
-        <v>1.88911</v>
+        <v>1.869747</v>
       </c>
       <c r="O32">
-        <v>0.2833664999999999</v>
+        <v>0.28046205</v>
       </c>
       <c r="P32">
-        <v>1.6057435</v>
+        <v>1.58928495</v>
       </c>
       <c r="Q32">
-        <v>2.7657435</v>
+        <v>2.74928495</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1241030371889723</v>
+        <v>0.125113092301054</v>
       </c>
       <c r="T32">
-        <v>1.020551069958355</v>
+        <v>1.033715474078009</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.252095921775206</v>
+        <v>4.114931537201812</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1015583336877273</v>
+        <v>0.1024575413431739</v>
       </c>
       <c r="C33">
-        <v>23.74335325113825</v>
+        <v>23.06005795688551</v>
       </c>
       <c r="D33">
-        <v>32.35835325113824</v>
+        <v>32.0100579568855</v>
       </c>
       <c r="E33">
-        <v>10.385</v>
+        <v>10.72</v>
       </c>
       <c r="F33">
-        <v>10.385</v>
+        <v>10.72</v>
       </c>
       <c r="G33">
         <v>1.77</v>
@@ -3993,45 +3993,45 @@
         <v>2.47</v>
       </c>
       <c r="M33">
-        <v>0.600253</v>
+        <v>0.6571360000000001</v>
       </c>
       <c r="N33">
-        <v>1.869747</v>
+        <v>1.812864</v>
       </c>
       <c r="O33">
-        <v>0.28046205</v>
+        <v>0.2719295999999999</v>
       </c>
       <c r="P33">
-        <v>1.58928495</v>
+        <v>1.5409344</v>
       </c>
       <c r="Q33">
-        <v>2.74928495</v>
+        <v>2.7009344</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.125113092301054</v>
+        <v>0.1261528549164322</v>
       </c>
       <c r="T33">
-        <v>1.033715474078009</v>
+        <v>1.047267066554123</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.114931537201812</v>
+        <v>3.758734873755204</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1024575413431739</v>
+        <v>0.1024344989986206</v>
       </c>
       <c r="C34">
-        <v>23.06005795688551</v>
+        <v>22.73388944991368</v>
       </c>
       <c r="D34">
-        <v>32.0100579568855</v>
+        <v>32.01888944991368</v>
       </c>
       <c r="E34">
-        <v>10.72</v>
+        <v>11.055</v>
       </c>
       <c r="F34">
-        <v>10.72</v>
+        <v>11.055</v>
       </c>
       <c r="G34">
         <v>1.77</v>
@@ -4075,28 +4075,28 @@
         <v>2.47</v>
       </c>
       <c r="M34">
-        <v>0.6571360000000001</v>
+        <v>0.6776715</v>
       </c>
       <c r="N34">
-        <v>1.812864</v>
+        <v>1.7923285</v>
       </c>
       <c r="O34">
-        <v>0.2719295999999999</v>
+        <v>0.2688492749999999</v>
       </c>
       <c r="P34">
-        <v>1.5409344</v>
+        <v>1.523479225</v>
       </c>
       <c r="Q34">
-        <v>2.7009344</v>
+        <v>2.683479225</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1261528549164322</v>
+        <v>0.1272236552218218</v>
       </c>
       <c r="T34">
-        <v>1.047267066554123</v>
+        <v>1.061223184178779</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.758734873755204</v>
+        <v>3.644833816974743</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1024344989986206</v>
+        <v>0.1024114566540673</v>
       </c>
       <c r="C35">
-        <v>22.73388944991368</v>
+        <v>22.40772581745934</v>
       </c>
       <c r="D35">
-        <v>32.01888944991368</v>
+        <v>32.02772581745934</v>
       </c>
       <c r="E35">
-        <v>11.055</v>
+        <v>11.39</v>
       </c>
       <c r="F35">
-        <v>11.055</v>
+        <v>11.39</v>
       </c>
       <c r="G35">
         <v>1.77</v>
@@ -4157,28 +4157,28 @@
         <v>2.47</v>
       </c>
       <c r="M35">
-        <v>0.6776715</v>
+        <v>0.698207</v>
       </c>
       <c r="N35">
-        <v>1.7923285</v>
+        <v>1.771793</v>
       </c>
       <c r="O35">
-        <v>0.2688492749999999</v>
+        <v>0.2657689499999999</v>
       </c>
       <c r="P35">
-        <v>1.523479225</v>
+        <v>1.50602405</v>
       </c>
       <c r="Q35">
-        <v>2.683479225</v>
+        <v>2.66602405</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1272236552218218</v>
+        <v>0.1283269040213141</v>
       </c>
       <c r="T35">
-        <v>1.061223184178779</v>
+        <v>1.075602214458727</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.644833816974743</v>
+        <v>3.537632822357839</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1024114566540673</v>
+        <v>0.103221414309514</v>
       </c>
       <c r="C36">
-        <v>22.40772581745934</v>
+        <v>21.76501936786185</v>
       </c>
       <c r="D36">
-        <v>32.02772581745934</v>
+        <v>31.72001936786185</v>
       </c>
       <c r="E36">
-        <v>11.39</v>
+        <v>11.725</v>
       </c>
       <c r="F36">
-        <v>11.39</v>
+        <v>11.725</v>
       </c>
       <c r="G36">
         <v>1.77</v>
@@ -4239,45 +4239,45 @@
         <v>2.47</v>
       </c>
       <c r="M36">
-        <v>0.698207</v>
+        <v>0.7515725000000001</v>
       </c>
       <c r="N36">
-        <v>1.771793</v>
+        <v>1.7184275</v>
       </c>
       <c r="O36">
-        <v>0.2657689499999999</v>
+        <v>0.257764125</v>
       </c>
       <c r="P36">
-        <v>1.50602405</v>
+        <v>1.460663375</v>
       </c>
       <c r="Q36">
-        <v>2.66602405</v>
+        <v>2.620663374999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1283269040213141</v>
+        <v>0.1294640989377138</v>
       </c>
       <c r="T36">
-        <v>1.075602214458727</v>
+        <v>1.090423676439596</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.537632822357839</v>
+        <v>3.286442758349992</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.103221414309514</v>
+        <v>0.1032221719649606</v>
       </c>
       <c r="C37">
-        <v>21.76501936786185</v>
+        <v>21.42973429920257</v>
       </c>
       <c r="D37">
-        <v>31.72001936786185</v>
+        <v>31.71973429920257</v>
       </c>
       <c r="E37">
-        <v>11.725</v>
+        <v>12.06</v>
       </c>
       <c r="F37">
-        <v>11.725</v>
+        <v>12.06</v>
       </c>
       <c r="G37">
         <v>1.77</v>
@@ -4321,28 +4321,28 @@
         <v>2.47</v>
       </c>
       <c r="M37">
-        <v>0.7515725000000001</v>
+        <v>0.7730460000000002</v>
       </c>
       <c r="N37">
-        <v>1.7184275</v>
+        <v>1.696953999999999</v>
       </c>
       <c r="O37">
-        <v>0.257764125</v>
+        <v>0.2545430999999999</v>
       </c>
       <c r="P37">
-        <v>1.460663375</v>
+        <v>1.4424109</v>
       </c>
       <c r="Q37">
-        <v>2.620663374999999</v>
+        <v>2.6024109</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1294640989377138</v>
+        <v>0.130636831195251</v>
       </c>
       <c r="T37">
-        <v>1.090423676439596</v>
+        <v>1.105708309107367</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.286442758349992</v>
+        <v>3.195152681729158</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1032221719649607</v>
+        <v>0.1032229296204073</v>
       </c>
       <c r="C38">
-        <v>21.42973429920257</v>
+        <v>21.09444923566709</v>
       </c>
       <c r="D38">
-        <v>31.71973429920257</v>
+        <v>31.71944923566709</v>
       </c>
       <c r="E38">
-        <v>12.06</v>
+        <v>12.395</v>
       </c>
       <c r="F38">
-        <v>12.06</v>
+        <v>12.395</v>
       </c>
       <c r="G38">
         <v>1.77</v>
@@ -4403,28 +4403,28 @@
         <v>2.47</v>
       </c>
       <c r="M38">
-        <v>0.773046</v>
+        <v>0.7945195</v>
       </c>
       <c r="N38">
-        <v>1.696954</v>
+        <v>1.6754805</v>
       </c>
       <c r="O38">
-        <v>0.2545431</v>
+        <v>0.2513220749999999</v>
       </c>
       <c r="P38">
-        <v>1.4424109</v>
+        <v>1.424158425</v>
       </c>
       <c r="Q38">
-        <v>2.6024109</v>
+        <v>2.584158425</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.130636831195251</v>
+        <v>0.1318467930482656</v>
       </c>
       <c r="T38">
-        <v>1.105708309107367</v>
+        <v>1.121478168209036</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.19515268172916</v>
+        <v>3.108797203844587</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1032229296204073</v>
+        <v>0.103223687275854</v>
       </c>
       <c r="C39">
-        <v>21.09444923566709</v>
+        <v>20.75916417725526</v>
       </c>
       <c r="D39">
-        <v>31.71944923566709</v>
+        <v>31.71916417725526</v>
       </c>
       <c r="E39">
-        <v>12.395</v>
+        <v>12.73</v>
       </c>
       <c r="F39">
-        <v>12.395</v>
+        <v>12.73</v>
       </c>
       <c r="G39">
         <v>1.77</v>
@@ -4485,28 +4485,28 @@
         <v>2.47</v>
       </c>
       <c r="M39">
-        <v>0.7945195</v>
+        <v>0.8159930000000001</v>
       </c>
       <c r="N39">
-        <v>1.6754805</v>
+        <v>1.654007</v>
       </c>
       <c r="O39">
-        <v>0.2513220749999999</v>
+        <v>0.2481010499999999</v>
       </c>
       <c r="P39">
-        <v>1.424158425</v>
+        <v>1.40590595</v>
       </c>
       <c r="Q39">
-        <v>2.584158425</v>
+        <v>2.565905949999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1318467930482656</v>
+        <v>0.1330957859287968</v>
       </c>
       <c r="T39">
-        <v>1.121478168209036</v>
+        <v>1.137756732443017</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.108797203844587</v>
+        <v>3.026986751111835</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.103223687275854</v>
+        <v>0.1058101449313007</v>
       </c>
       <c r="C40">
-        <v>20.75916417725526</v>
+        <v>19.48001605318968</v>
       </c>
       <c r="D40">
-        <v>31.71916417725526</v>
+        <v>30.77501605318967</v>
       </c>
       <c r="E40">
-        <v>12.73</v>
+        <v>13.065</v>
       </c>
       <c r="F40">
-        <v>12.73</v>
+        <v>13.065</v>
       </c>
       <c r="G40">
         <v>1.77</v>
@@ -4567,45 +4567,45 @@
         <v>2.47</v>
       </c>
       <c r="M40">
-        <v>0.8159930000000001</v>
+        <v>0.9393735000000002</v>
       </c>
       <c r="N40">
-        <v>1.654007</v>
+        <v>1.530626499999999</v>
       </c>
       <c r="O40">
-        <v>0.2481010499999999</v>
+        <v>0.2295939749999999</v>
       </c>
       <c r="P40">
-        <v>1.40590595</v>
+        <v>1.301032525</v>
       </c>
       <c r="Q40">
-        <v>2.565905949999999</v>
+        <v>2.461032524999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1330957859287968</v>
+        <v>0.1343857293955749</v>
       </c>
       <c r="T40">
-        <v>1.137756732443017</v>
+        <v>1.154569020094505</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.026986751111835</v>
+        <v>2.629412049626692</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1058101449313007</v>
+        <v>0.1058772025867474</v>
       </c>
       <c r="C41">
-        <v>19.48001605318968</v>
+        <v>19.12128458243077</v>
       </c>
       <c r="D41">
-        <v>30.77501605318967</v>
+        <v>30.75128458243077</v>
       </c>
       <c r="E41">
-        <v>13.065</v>
+        <v>13.4</v>
       </c>
       <c r="F41">
-        <v>13.065</v>
+        <v>13.4</v>
       </c>
       <c r="G41">
         <v>1.77</v>
@@ -4649,28 +4649,28 @@
         <v>2.47</v>
       </c>
       <c r="M41">
-        <v>0.9393735000000002</v>
+        <v>0.9634600000000001</v>
       </c>
       <c r="N41">
-        <v>1.530626499999999</v>
+        <v>1.50654</v>
       </c>
       <c r="O41">
-        <v>0.2295939749999999</v>
+        <v>0.225981</v>
       </c>
       <c r="P41">
-        <v>1.301032525</v>
+        <v>1.280559</v>
       </c>
       <c r="Q41">
-        <v>2.461032524999999</v>
+        <v>2.440558999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1343857293955749</v>
+        <v>0.1357186709779123</v>
       </c>
       <c r="T41">
-        <v>1.154569020094505</v>
+        <v>1.171941717334376</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.629412049626692</v>
+        <v>2.563676748386025</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1058772025867474</v>
+        <v>0.105944260242194</v>
       </c>
       <c r="C42">
-        <v>19.12128458243077</v>
+        <v>18.76258968346453</v>
       </c>
       <c r="D42">
-        <v>30.75128458243077</v>
+        <v>30.72758968346453</v>
       </c>
       <c r="E42">
-        <v>13.4</v>
+        <v>13.735</v>
       </c>
       <c r="F42">
-        <v>13.4</v>
+        <v>13.735</v>
       </c>
       <c r="G42">
         <v>1.77</v>
@@ -4731,28 +4731,28 @@
         <v>2.47</v>
       </c>
       <c r="M42">
-        <v>0.9634600000000001</v>
+        <v>0.9875465000000002</v>
       </c>
       <c r="N42">
-        <v>1.50654</v>
+        <v>1.4824535</v>
       </c>
       <c r="O42">
-        <v>0.225981</v>
+        <v>0.2223680249999999</v>
       </c>
       <c r="P42">
-        <v>1.280559</v>
+        <v>1.260085475</v>
       </c>
       <c r="Q42">
-        <v>2.440558999999999</v>
+        <v>2.420085475</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1357186709779123</v>
+        <v>0.1370967970206679</v>
       </c>
       <c r="T42">
-        <v>1.171941717334376</v>
+        <v>1.18990331956543</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.563676748386025</v>
+        <v>2.501148047205878</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.105944260242194</v>
+        <v>0.1074036178976407</v>
       </c>
       <c r="C43">
-        <v>18.76258968346453</v>
+        <v>17.92081932005529</v>
       </c>
       <c r="D43">
-        <v>30.72758968346453</v>
+        <v>30.22081932005529</v>
       </c>
       <c r="E43">
-        <v>13.735</v>
+        <v>14.07</v>
       </c>
       <c r="F43">
-        <v>13.735</v>
+        <v>14.07</v>
       </c>
       <c r="G43">
         <v>1.77</v>
@@ -4813,45 +4813,45 @@
         <v>2.47</v>
       </c>
       <c r="M43">
-        <v>0.9875465000000002</v>
+        <v>1.066506</v>
       </c>
       <c r="N43">
-        <v>1.4824535</v>
+        <v>1.403494</v>
       </c>
       <c r="O43">
-        <v>0.2223680249999999</v>
+        <v>0.2105240999999999</v>
       </c>
       <c r="P43">
-        <v>1.260085475</v>
+        <v>1.1929699</v>
       </c>
       <c r="Q43">
-        <v>2.420085475</v>
+        <v>2.3529699</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1370967970206679</v>
+        <v>0.1385224446511047</v>
       </c>
       <c r="T43">
-        <v>1.18990331956543</v>
+        <v>1.208484287390657</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.501148047205878</v>
+        <v>2.315973843560186</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1074036178976407</v>
+        <v>0.1075038255530874</v>
       </c>
       <c r="C44">
-        <v>17.92081932005529</v>
+        <v>17.5516342426975</v>
       </c>
       <c r="D44">
-        <v>30.22081932005529</v>
+        <v>30.1866342426975</v>
       </c>
       <c r="E44">
-        <v>14.07</v>
+        <v>14.405</v>
       </c>
       <c r="F44">
-        <v>14.07</v>
+        <v>14.405</v>
       </c>
       <c r="G44">
         <v>1.77</v>
@@ -4895,28 +4895,28 @@
         <v>2.47</v>
       </c>
       <c r="M44">
-        <v>1.066506</v>
+        <v>1.091899</v>
       </c>
       <c r="N44">
-        <v>1.403494</v>
+        <v>1.378101</v>
       </c>
       <c r="O44">
-        <v>0.2105240999999999</v>
+        <v>0.20671515</v>
       </c>
       <c r="P44">
-        <v>1.1929699</v>
+        <v>1.17138585</v>
       </c>
       <c r="Q44">
-        <v>2.3529699</v>
+        <v>2.33138585</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1385224446511047</v>
+        <v>0.1399981150054165</v>
       </c>
       <c r="T44">
-        <v>1.208484287390657</v>
+        <v>1.227717218999226</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.315973843560186</v>
+        <v>2.262113986733205</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1075038255530874</v>
+        <v>0.1076040332085341</v>
       </c>
       <c r="C45">
-        <v>17.5516342426975</v>
+        <v>17.18252641665976</v>
       </c>
       <c r="D45">
-        <v>30.1866342426975</v>
+        <v>30.15252641665976</v>
       </c>
       <c r="E45">
-        <v>14.405</v>
+        <v>14.74</v>
       </c>
       <c r="F45">
-        <v>14.405</v>
+        <v>14.74</v>
       </c>
       <c r="G45">
         <v>1.77</v>
@@ -4977,28 +4977,28 @@
         <v>2.47</v>
       </c>
       <c r="M45">
-        <v>1.091899</v>
+        <v>1.117292</v>
       </c>
       <c r="N45">
-        <v>1.378101</v>
+        <v>1.352708</v>
       </c>
       <c r="O45">
-        <v>0.20671515</v>
+        <v>0.2029061999999999</v>
       </c>
       <c r="P45">
-        <v>1.17138585</v>
+        <v>1.1498018</v>
       </c>
       <c r="Q45">
-        <v>2.33138585</v>
+        <v>2.3098018</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1399981150054165</v>
+        <v>0.1415264878723823</v>
       </c>
       <c r="T45">
-        <v>1.227717218999226</v>
+        <v>1.247637041022387</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.262113986733205</v>
+        <v>2.210702305216541</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1076040332085341</v>
+        <v>0.1077042408639808</v>
       </c>
       <c r="C46">
-        <v>17.18252641665976</v>
+        <v>16.81349558037922</v>
       </c>
       <c r="D46">
-        <v>30.15252641665976</v>
+        <v>30.11849558037922</v>
       </c>
       <c r="E46">
-        <v>14.74</v>
+        <v>15.075</v>
       </c>
       <c r="F46">
-        <v>14.74</v>
+        <v>15.075</v>
       </c>
       <c r="G46">
         <v>1.77</v>
@@ -5059,28 +5059,28 @@
         <v>2.47</v>
       </c>
       <c r="M46">
-        <v>1.117292</v>
+        <v>1.142685</v>
       </c>
       <c r="N46">
-        <v>1.352708</v>
+        <v>1.327315</v>
       </c>
       <c r="O46">
-        <v>0.2029061999999999</v>
+        <v>0.1990972499999999</v>
       </c>
       <c r="P46">
-        <v>1.1498018</v>
+        <v>1.12821775</v>
       </c>
       <c r="Q46">
-        <v>2.3098018</v>
+        <v>2.288217749999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1415264878723823</v>
+        <v>0.1431104379345105</v>
       </c>
       <c r="T46">
-        <v>1.247637041022387</v>
+        <v>1.268281220210026</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.210702305216541</v>
+        <v>2.16157558732284</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1077042408639808</v>
+        <v>0.1078044485194275</v>
       </c>
       <c r="C47">
-        <v>16.81349558037922</v>
+        <v>16.44454147347249</v>
       </c>
       <c r="D47">
-        <v>30.11849558037922</v>
+        <v>30.08454147347249</v>
       </c>
       <c r="E47">
-        <v>15.075</v>
+        <v>15.41</v>
       </c>
       <c r="F47">
-        <v>15.075</v>
+        <v>15.41</v>
       </c>
       <c r="G47">
         <v>1.77</v>
@@ -5141,28 +5141,28 @@
         <v>2.47</v>
       </c>
       <c r="M47">
-        <v>1.142685</v>
+        <v>1.168078</v>
       </c>
       <c r="N47">
-        <v>1.327315</v>
+        <v>1.301922</v>
       </c>
       <c r="O47">
-        <v>0.1990972499999999</v>
+        <v>0.1952882999999999</v>
       </c>
       <c r="P47">
-        <v>1.12821775</v>
+        <v>1.1066337</v>
       </c>
       <c r="Q47">
-        <v>2.288217749999999</v>
+        <v>2.2666337</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1431104379345105</v>
+        <v>0.1447530528137545</v>
       </c>
       <c r="T47">
-        <v>1.268281220210026</v>
+        <v>1.289689998626837</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.16157558732284</v>
+        <v>2.114584813685387</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1078044485194275</v>
+        <v>0.1079046561748741</v>
       </c>
       <c r="C48">
-        <v>16.44454147347249</v>
+        <v>16.07566383672907</v>
       </c>
       <c r="D48">
-        <v>30.08454147347249</v>
+        <v>30.05066383672907</v>
       </c>
       <c r="E48">
-        <v>15.41</v>
+        <v>15.745</v>
       </c>
       <c r="F48">
-        <v>15.41</v>
+        <v>15.745</v>
       </c>
       <c r="G48">
         <v>1.77</v>
@@ -5223,28 +5223,28 @@
         <v>2.47</v>
       </c>
       <c r="M48">
-        <v>1.168078</v>
+        <v>1.193471</v>
       </c>
       <c r="N48">
-        <v>1.301922</v>
+        <v>1.276529</v>
       </c>
       <c r="O48">
-        <v>0.1952882999999999</v>
+        <v>0.1914793499999999</v>
       </c>
       <c r="P48">
-        <v>1.1066337</v>
+        <v>1.08504965</v>
       </c>
       <c r="Q48">
-        <v>2.2666337</v>
+        <v>2.245049649999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1447530528137545</v>
+        <v>0.1464576531601399</v>
       </c>
       <c r="T48">
-        <v>1.289689998626837</v>
+        <v>1.311906655474471</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.114584813685387</v>
+        <v>2.069593647436762</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1079046561748741</v>
+        <v>0.1080048638303208</v>
       </c>
       <c r="C49">
-        <v>16.07566383672907</v>
+        <v>15.7068624121047</v>
       </c>
       <c r="D49">
-        <v>30.05066383672907</v>
+        <v>30.0168624121047</v>
       </c>
       <c r="E49">
-        <v>15.745</v>
+        <v>16.08</v>
       </c>
       <c r="F49">
-        <v>15.745</v>
+        <v>16.08</v>
       </c>
       <c r="G49">
         <v>1.77</v>
@@ -5305,28 +5305,28 @@
         <v>2.47</v>
       </c>
       <c r="M49">
-        <v>1.193471</v>
+        <v>1.218864</v>
       </c>
       <c r="N49">
-        <v>1.276529</v>
+        <v>1.251136</v>
       </c>
       <c r="O49">
-        <v>0.1914793499999999</v>
+        <v>0.1876703999999999</v>
       </c>
       <c r="P49">
-        <v>1.08504965</v>
+        <v>1.0634656</v>
       </c>
       <c r="Q49">
-        <v>2.245049649999999</v>
+        <v>2.223465599999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1464576531601399</v>
+        <v>0.1482278150583092</v>
       </c>
       <c r="T49">
-        <v>1.311906655474471</v>
+        <v>1.334977799123938</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.069593647436762</v>
+        <v>2.026477113115162</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1080048638303208</v>
+        <v>0.1140193714857675</v>
       </c>
       <c r="C50">
-        <v>15.70686241210471</v>
+        <v>13.47352809547062</v>
       </c>
       <c r="D50">
-        <v>30.01686241210471</v>
+        <v>28.11852809547062</v>
       </c>
       <c r="E50">
-        <v>16.08</v>
+        <v>16.415</v>
       </c>
       <c r="F50">
-        <v>16.08</v>
+        <v>16.415</v>
       </c>
       <c r="G50">
         <v>1.77</v>
@@ -5387,45 +5387,45 @@
         <v>2.47</v>
       </c>
       <c r="M50">
-        <v>1.218864</v>
+        <v>1.47735</v>
       </c>
       <c r="N50">
-        <v>1.251136</v>
+        <v>0.9926499999999998</v>
       </c>
       <c r="O50">
-        <v>0.1876704</v>
+        <v>0.1488975</v>
       </c>
       <c r="P50">
-        <v>1.0634656</v>
+        <v>0.8437524999999999</v>
       </c>
       <c r="Q50">
-        <v>2.2234656</v>
+        <v>2.0037525</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1482278150583092</v>
+        <v>0.1500673950701323</v>
       </c>
       <c r="T50">
-        <v>1.334977799123938</v>
+        <v>1.358953693504755</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.026477113115163</v>
+        <v>1.671912546112972</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1140193714857675</v>
+        <v>0.1142402791412142</v>
       </c>
       <c r="C51">
-        <v>13.47352809547062</v>
+        <v>13.0733647987783</v>
       </c>
       <c r="D51">
-        <v>28.11852809547062</v>
+        <v>28.0533647987783</v>
       </c>
       <c r="E51">
-        <v>16.415</v>
+        <v>16.75</v>
       </c>
       <c r="F51">
-        <v>16.415</v>
+        <v>16.75</v>
       </c>
       <c r="G51">
         <v>1.77</v>
@@ -5469,28 +5469,28 @@
         <v>2.47</v>
       </c>
       <c r="M51">
-        <v>1.47735</v>
+        <v>1.5075</v>
       </c>
       <c r="N51">
-        <v>0.9926499999999998</v>
+        <v>0.9624999999999999</v>
       </c>
       <c r="O51">
-        <v>0.1488975</v>
+        <v>0.144375</v>
       </c>
       <c r="P51">
-        <v>0.8437524999999999</v>
+        <v>0.818125</v>
       </c>
       <c r="Q51">
-        <v>2.0037525</v>
+        <v>1.978125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1500673950701323</v>
+        <v>0.1519805582824283</v>
       </c>
       <c r="T51">
-        <v>1.358953693504755</v>
+        <v>1.383888623660806</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.671912546112972</v>
+        <v>1.638474295190713</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1142402791412142</v>
+        <v>0.1144611867966608</v>
       </c>
       <c r="C52">
-        <v>13.0733647987783</v>
+        <v>12.67350282920293</v>
       </c>
       <c r="D52">
-        <v>28.0533647987783</v>
+        <v>27.98850282920293</v>
       </c>
       <c r="E52">
-        <v>16.75</v>
+        <v>17.085</v>
       </c>
       <c r="F52">
-        <v>16.75</v>
+        <v>17.085</v>
       </c>
       <c r="G52">
         <v>1.77</v>
@@ -5551,28 +5551,28 @@
         <v>2.47</v>
       </c>
       <c r="M52">
-        <v>1.5075</v>
+        <v>1.53765</v>
       </c>
       <c r="N52">
-        <v>0.9624999999999999</v>
+        <v>0.9323499999999998</v>
       </c>
       <c r="O52">
-        <v>0.144375</v>
+        <v>0.1398525</v>
       </c>
       <c r="P52">
-        <v>0.818125</v>
+        <v>0.7924974999999999</v>
       </c>
       <c r="Q52">
-        <v>1.978125</v>
+        <v>1.9524975</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1519805582824283</v>
+        <v>0.1539718097891038</v>
       </c>
       <c r="T52">
-        <v>1.383888623660806</v>
+        <v>1.409841306068124</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.638474295190713</v>
+        <v>1.606347348226189</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1144611867966608</v>
+        <v>0.1146820944521075</v>
       </c>
       <c r="C53">
-        <v>12.67350282920293</v>
+        <v>12.27394010147746</v>
       </c>
       <c r="D53">
-        <v>27.98850282920293</v>
+        <v>27.92394010147746</v>
       </c>
       <c r="E53">
-        <v>17.085</v>
+        <v>17.42</v>
       </c>
       <c r="F53">
-        <v>17.085</v>
+        <v>17.42</v>
       </c>
       <c r="G53">
         <v>1.77</v>
@@ -5633,28 +5633,28 @@
         <v>2.47</v>
       </c>
       <c r="M53">
-        <v>1.53765</v>
+        <v>1.5678</v>
       </c>
       <c r="N53">
-        <v>0.9323499999999998</v>
+        <v>0.9021999999999997</v>
       </c>
       <c r="O53">
-        <v>0.1398525</v>
+        <v>0.13533</v>
       </c>
       <c r="P53">
-        <v>0.7924974999999999</v>
+        <v>0.7668699999999997</v>
       </c>
       <c r="Q53">
-        <v>1.9524975</v>
+        <v>1.92687</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1539718097891038</v>
+        <v>0.1560460301085574</v>
       </c>
       <c r="T53">
-        <v>1.409841306068124</v>
+        <v>1.436875350242414</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.606347348226189</v>
+        <v>1.575456053067993</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1146820944521075</v>
+        <v>0.1149030021075542</v>
       </c>
       <c r="C54">
-        <v>12.27394010147746</v>
+        <v>11.87467454953143</v>
       </c>
       <c r="D54">
-        <v>27.92394010147746</v>
+        <v>27.85967454953143</v>
       </c>
       <c r="E54">
-        <v>17.42</v>
+        <v>17.755</v>
       </c>
       <c r="F54">
-        <v>17.42</v>
+        <v>17.755</v>
       </c>
       <c r="G54">
         <v>1.77</v>
@@ -5715,28 +5715,28 @@
         <v>2.47</v>
       </c>
       <c r="M54">
-        <v>1.5678</v>
+        <v>1.59795</v>
       </c>
       <c r="N54">
-        <v>0.9021999999999997</v>
+        <v>0.8720499999999995</v>
       </c>
       <c r="O54">
-        <v>0.13533</v>
+        <v>0.1308074999999999</v>
       </c>
       <c r="P54">
-        <v>0.7668699999999997</v>
+        <v>0.7412424999999996</v>
       </c>
       <c r="Q54">
-        <v>1.92687</v>
+        <v>1.9012425</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1560460301085574</v>
+        <v>0.1582085151224558</v>
       </c>
       <c r="T54">
-        <v>1.436875350242414</v>
+        <v>1.465059779275183</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.575456053067993</v>
+        <v>1.54573046716105</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1149030021075542</v>
+        <v>0.1151239097630009</v>
       </c>
       <c r="C55">
-        <v>11.87467454953143</v>
+        <v>11.47570412627055</v>
       </c>
       <c r="D55">
-        <v>27.85967454953143</v>
+        <v>27.79570412627055</v>
       </c>
       <c r="E55">
-        <v>17.755</v>
+        <v>18.09</v>
       </c>
       <c r="F55">
-        <v>17.755</v>
+        <v>18.09</v>
       </c>
       <c r="G55">
         <v>1.77</v>
@@ -5797,28 +5797,28 @@
         <v>2.47</v>
       </c>
       <c r="M55">
-        <v>1.59795</v>
+        <v>1.6281</v>
       </c>
       <c r="N55">
-        <v>0.8720499999999995</v>
+        <v>0.8418999999999999</v>
       </c>
       <c r="O55">
-        <v>0.1308074999999999</v>
+        <v>0.126285</v>
       </c>
       <c r="P55">
-        <v>0.7412424999999996</v>
+        <v>0.7156149999999999</v>
       </c>
       <c r="Q55">
-        <v>1.9012425</v>
+        <v>1.875615</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1582085151224558</v>
+        <v>0.160465021223915</v>
       </c>
       <c r="T55">
-        <v>1.465059779275183</v>
+        <v>1.4944696182659</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.54573046716105</v>
+        <v>1.51710582888029</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1151239097630009</v>
+        <v>0.1433611456867316</v>
       </c>
       <c r="C56">
-        <v>11.47570412627055</v>
+        <v>4.833681709250204</v>
       </c>
       <c r="D56">
-        <v>27.79570412627055</v>
+        <v>21.4886817092502</v>
       </c>
       <c r="E56">
-        <v>18.09</v>
+        <v>18.425</v>
       </c>
       <c r="F56">
-        <v>18.09</v>
+        <v>18.425</v>
       </c>
       <c r="G56">
         <v>1.77</v>
@@ -5879,45 +5879,45 @@
         <v>2.47</v>
       </c>
       <c r="M56">
-        <v>1.6281</v>
+        <v>2.70479</v>
       </c>
       <c r="N56">
-        <v>0.8418999999999999</v>
+        <v>-0.2347900000000007</v>
       </c>
       <c r="O56">
-        <v>0.126285</v>
+        <v>-0.0352185000000001</v>
       </c>
       <c r="P56">
-        <v>0.7156149999999999</v>
+        <v>-0.1995715000000006</v>
       </c>
       <c r="Q56">
-        <v>1.875615</v>
+        <v>0.9604284999999992</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.160465021223915</v>
+        <v>0.163735215953931</v>
       </c>
       <c r="T56">
-        <v>1.4944696182659</v>
+        <v>1.537091218276583</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.15</v>
+        <v>0.1369792109553791</v>
       </c>
       <c r="W56">
-        <v>0.0765</v>
+        <v>0.1266914518317503</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.51710582888029</v>
+        <v>0.9131947397025275</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1433611456867316</v>
+        <v>0.1443711456867317</v>
       </c>
       <c r="C57">
-        <v>4.833681709250204</v>
+        <v>4.325682100698039</v>
       </c>
       <c r="D57">
-        <v>21.4886817092502</v>
+        <v>21.31568210069804</v>
       </c>
       <c r="E57">
-        <v>18.425</v>
+        <v>18.76</v>
       </c>
       <c r="F57">
-        <v>18.425</v>
+        <v>18.76</v>
       </c>
       <c r="G57">
         <v>1.77</v>
@@ -5961,37 +5961,37 @@
         <v>2.47</v>
       </c>
       <c r="M57">
-        <v>2.70479</v>
+        <v>2.753968</v>
       </c>
       <c r="N57">
-        <v>-0.2347900000000007</v>
+        <v>-0.2839680000000007</v>
       </c>
       <c r="O57">
-        <v>-0.0352185000000001</v>
+        <v>-0.0425952000000001</v>
       </c>
       <c r="P57">
-        <v>-0.1995715000000006</v>
+        <v>-0.2413728000000006</v>
       </c>
       <c r="Q57">
-        <v>0.9604284999999992</v>
+        <v>0.9186271999999993</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.163735215953931</v>
+        <v>0.1664155617710658</v>
       </c>
       <c r="T57">
-        <v>1.537091218276583</v>
+        <v>1.572025109601051</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1369792109553791</v>
+        <v>0.1345331536168902</v>
       </c>
       <c r="W57">
-        <v>0.1266914518317503</v>
+        <v>0.1270505330490405</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9131947397025275</v>
+        <v>0.8968876907792681</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1443711456867317</v>
+        <v>0.1453811456867316</v>
       </c>
       <c r="C58">
-        <v>4.325682100698039</v>
+        <v>3.820445792382841</v>
       </c>
       <c r="D58">
-        <v>21.31568210069804</v>
+        <v>21.14544579238284</v>
       </c>
       <c r="E58">
-        <v>18.76</v>
+        <v>19.095</v>
       </c>
       <c r="F58">
-        <v>18.76</v>
+        <v>19.095</v>
       </c>
       <c r="G58">
         <v>1.77</v>
@@ -6043,37 +6043,37 @@
         <v>2.47</v>
       </c>
       <c r="M58">
-        <v>2.753968</v>
+        <v>2.803146000000001</v>
       </c>
       <c r="N58">
-        <v>-0.2839680000000007</v>
+        <v>-0.3331460000000011</v>
       </c>
       <c r="O58">
-        <v>-0.0425952000000001</v>
+        <v>-0.04997190000000016</v>
       </c>
       <c r="P58">
-        <v>-0.2413728000000006</v>
+        <v>-0.2831741000000009</v>
       </c>
       <c r="Q58">
-        <v>0.9186271999999993</v>
+        <v>0.876825899999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1664155617710658</v>
+        <v>0.1692205748355092</v>
       </c>
       <c r="T58">
-        <v>1.572025109601051</v>
+        <v>1.608583833080145</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1345331536168902</v>
+        <v>0.1321729228516816</v>
       </c>
       <c r="W58">
-        <v>0.1270505330490405</v>
+        <v>0.1273970149253731</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8968876907792681</v>
+        <v>0.8811528190112107</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1453811456867316</v>
+        <v>0.1463911456867317</v>
       </c>
       <c r="C59">
-        <v>3.820445792382841</v>
+        <v>3.317907102118411</v>
       </c>
       <c r="D59">
-        <v>21.14544579238284</v>
+        <v>20.97790710211842</v>
       </c>
       <c r="E59">
-        <v>19.095</v>
+        <v>19.43</v>
       </c>
       <c r="F59">
-        <v>19.095</v>
+        <v>19.43</v>
       </c>
       <c r="G59">
         <v>1.77</v>
@@ -6125,37 +6125,37 @@
         <v>2.47</v>
       </c>
       <c r="M59">
-        <v>2.803146000000001</v>
+        <v>2.852324000000001</v>
       </c>
       <c r="N59">
-        <v>-0.3331460000000011</v>
+        <v>-0.382324000000001</v>
       </c>
       <c r="O59">
-        <v>-0.04997190000000016</v>
+        <v>-0.05734860000000015</v>
       </c>
       <c r="P59">
-        <v>-0.2831741000000009</v>
+        <v>-0.3249754000000009</v>
       </c>
       <c r="Q59">
-        <v>0.876825899999999</v>
+        <v>0.835024599999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1692205748355092</v>
+        <v>0.1721591599506404</v>
       </c>
       <c r="T59">
-        <v>1.608583833080145</v>
+        <v>1.646883448153482</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1321729228516816</v>
+        <v>0.1298940793542388</v>
       </c>
       <c r="W59">
-        <v>0.1273970149253731</v>
+        <v>0.1277315491507978</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8811528190112107</v>
+        <v>0.8659605290282587</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1463911456867317</v>
+        <v>0.1474011456867317</v>
       </c>
       <c r="C60">
-        <v>3.317907102118415</v>
+        <v>2.818002412996186</v>
       </c>
       <c r="D60">
-        <v>20.97790710211842</v>
+        <v>20.81300241299619</v>
       </c>
       <c r="E60">
-        <v>19.43</v>
+        <v>19.765</v>
       </c>
       <c r="F60">
-        <v>19.43</v>
+        <v>19.765</v>
       </c>
       <c r="G60">
         <v>1.77</v>
@@ -6207,37 +6207,37 @@
         <v>2.47</v>
       </c>
       <c r="M60">
-        <v>2.852324</v>
+        <v>2.901502</v>
       </c>
       <c r="N60">
-        <v>-0.3823240000000006</v>
+        <v>-0.4315020000000005</v>
       </c>
       <c r="O60">
-        <v>-0.05734860000000008</v>
+        <v>-0.06472530000000007</v>
       </c>
       <c r="P60">
-        <v>-0.3249754000000005</v>
+        <v>-0.3667767000000004</v>
       </c>
       <c r="Q60">
-        <v>0.8350245999999995</v>
+        <v>0.7932232999999995</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1721591599506404</v>
+        <v>0.1752410906811438</v>
       </c>
       <c r="T60">
-        <v>1.646883448153482</v>
+        <v>1.687051337132835</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1298940793542388</v>
+        <v>0.1276924847889127</v>
       </c>
       <c r="W60">
-        <v>0.1277315491507978</v>
+        <v>0.1280547432329876</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8659605290282588</v>
+        <v>0.851283231926085</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1474011456867317</v>
+        <v>0.1484111456867316</v>
       </c>
       <c r="C61">
-        <v>2.818002412996186</v>
+        <v>2.320670092843908</v>
       </c>
       <c r="D61">
-        <v>20.81300241299619</v>
+        <v>20.65067009284391</v>
       </c>
       <c r="E61">
-        <v>19.765</v>
+        <v>20.1</v>
       </c>
       <c r="F61">
-        <v>19.765</v>
+        <v>20.1</v>
       </c>
       <c r="G61">
         <v>1.77</v>
@@ -6289,37 +6289,37 @@
         <v>2.47</v>
       </c>
       <c r="M61">
-        <v>2.901502</v>
+        <v>2.95068</v>
       </c>
       <c r="N61">
-        <v>-0.4315020000000005</v>
+        <v>-0.48068</v>
       </c>
       <c r="O61">
-        <v>-0.06472530000000007</v>
+        <v>-0.072102</v>
       </c>
       <c r="P61">
-        <v>-0.3667767000000004</v>
+        <v>-0.408578</v>
       </c>
       <c r="Q61">
-        <v>0.7932232999999995</v>
+        <v>0.7514219999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1752410906811438</v>
+        <v>0.1784771179481724</v>
       </c>
       <c r="T61">
-        <v>1.687051337132835</v>
+        <v>1.729227620561156</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1276924847889127</v>
+        <v>0.1255642767090976</v>
       </c>
       <c r="W61">
-        <v>0.1280547432329876</v>
+        <v>0.1283671641791045</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.851283231926085</v>
+        <v>0.8370951780606504</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1484111456867316</v>
+        <v>0.1494211456867316</v>
       </c>
       <c r="C62">
-        <v>2.320670092843908</v>
+        <v>1.825850417424231</v>
       </c>
       <c r="D62">
-        <v>20.65067009284391</v>
+        <v>20.49085041742423</v>
       </c>
       <c r="E62">
-        <v>20.1</v>
+        <v>20.435</v>
       </c>
       <c r="F62">
-        <v>20.1</v>
+        <v>20.435</v>
       </c>
       <c r="G62">
         <v>1.77</v>
@@ -6371,37 +6371,37 @@
         <v>2.47</v>
       </c>
       <c r="M62">
-        <v>2.95068</v>
+        <v>2.999858</v>
       </c>
       <c r="N62">
-        <v>-0.48068</v>
+        <v>-0.5298580000000004</v>
       </c>
       <c r="O62">
-        <v>-0.072102</v>
+        <v>-0.07947870000000005</v>
       </c>
       <c r="P62">
-        <v>-0.408578</v>
+        <v>-0.4503793000000003</v>
       </c>
       <c r="Q62">
-        <v>0.7514219999999999</v>
+        <v>0.7096206999999997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1784771179481724</v>
+        <v>0.1818790953314589</v>
       </c>
       <c r="T62">
-        <v>1.729227620561156</v>
+        <v>1.773566790319135</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1255642767090976</v>
+        <v>0.1235058459433746</v>
       </c>
       <c r="W62">
-        <v>0.1283671641791045</v>
+        <v>0.1286693418155126</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8370951780606504</v>
+        <v>0.8233723062891642</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1494211456867316</v>
+        <v>0.1504311456867317</v>
       </c>
       <c r="C63">
-        <v>1.825850417424231</v>
+        <v>1.333485497172326</v>
       </c>
       <c r="D63">
-        <v>20.49085041742423</v>
+        <v>20.33348549717233</v>
       </c>
       <c r="E63">
-        <v>20.435</v>
+        <v>20.77</v>
       </c>
       <c r="F63">
-        <v>20.435</v>
+        <v>20.77</v>
       </c>
       <c r="G63">
         <v>1.77</v>
@@ -6453,37 +6453,37 @@
         <v>2.47</v>
       </c>
       <c r="M63">
-        <v>2.999858</v>
+        <v>3.049036</v>
       </c>
       <c r="N63">
-        <v>-0.5298580000000004</v>
+        <v>-0.5790360000000003</v>
       </c>
       <c r="O63">
-        <v>-0.07947870000000005</v>
+        <v>-0.08685540000000004</v>
       </c>
       <c r="P63">
-        <v>-0.4503793000000003</v>
+        <v>-0.4921806000000003</v>
       </c>
       <c r="Q63">
-        <v>0.7096206999999997</v>
+        <v>0.6678193999999996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1818790953314589</v>
+        <v>0.1854601241559709</v>
       </c>
       <c r="T63">
-        <v>1.773566790319135</v>
+        <v>1.82023960059069</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1235058459433746</v>
+        <v>0.1215138161700944</v>
       </c>
       <c r="W63">
-        <v>0.1286693418155126</v>
+        <v>0.1289617717862302</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8233723062891642</v>
+        <v>0.8100921078006293</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1504311456867317</v>
+        <v>0.1866239876002725</v>
       </c>
       <c r="C64">
-        <v>1.333485497172326</v>
+        <v>-3.389676006909152</v>
       </c>
       <c r="D64">
-        <v>20.33348549717233</v>
+        <v>15.94532399309085</v>
       </c>
       <c r="E64">
-        <v>20.77</v>
+        <v>21.105</v>
       </c>
       <c r="F64">
-        <v>20.77</v>
+        <v>21.105</v>
       </c>
       <c r="G64">
         <v>1.77</v>
@@ -6535,45 +6535,45 @@
         <v>2.47</v>
       </c>
       <c r="M64">
-        <v>3.049036</v>
+        <v>4.237884</v>
       </c>
       <c r="N64">
-        <v>-0.5790360000000003</v>
+        <v>-1.767884</v>
       </c>
       <c r="O64">
-        <v>-0.08685540000000004</v>
+        <v>-0.2651826</v>
       </c>
       <c r="P64">
-        <v>-0.4921806000000003</v>
+        <v>-1.5027014</v>
       </c>
       <c r="Q64">
-        <v>0.6678193999999996</v>
+        <v>-0.3427014000000004</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1854601241559709</v>
+        <v>0.1923775380886752</v>
       </c>
       <c r="T64">
-        <v>1.82023960059069</v>
+        <v>1.910396693390667</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1215138161700944</v>
+        <v>0.08742570584754088</v>
       </c>
       <c r="W64">
-        <v>0.1289617717862302</v>
+        <v>0.1832449182658138</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8100921078006293</v>
+        <v>0.5828380389836059</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1866239876002725</v>
+        <v>0.1881739876002725</v>
       </c>
       <c r="C65">
-        <v>-3.389676006909152</v>
+        <v>-3.870697804725236</v>
       </c>
       <c r="D65">
-        <v>15.94532399309085</v>
+        <v>15.79930219527476</v>
       </c>
       <c r="E65">
-        <v>21.105</v>
+        <v>21.44</v>
       </c>
       <c r="F65">
-        <v>21.105</v>
+        <v>21.44</v>
       </c>
       <c r="G65">
         <v>1.77</v>
@@ -6617,37 +6617,37 @@
         <v>2.47</v>
       </c>
       <c r="M65">
-        <v>4.237884</v>
+        <v>4.305152000000001</v>
       </c>
       <c r="N65">
-        <v>-1.767884</v>
+        <v>-1.835152000000001</v>
       </c>
       <c r="O65">
-        <v>-0.2651826</v>
+        <v>-0.2752728000000001</v>
       </c>
       <c r="P65">
-        <v>-1.5027014</v>
+        <v>-1.559879200000001</v>
       </c>
       <c r="Q65">
-        <v>-0.3427014000000004</v>
+        <v>-0.3998792000000007</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1923775380886752</v>
+        <v>0.1964491363689162</v>
       </c>
       <c r="T65">
-        <v>1.910396693390667</v>
+        <v>1.963463268207075</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08742570584754088</v>
+        <v>0.08605967919367304</v>
       </c>
       <c r="W65">
-        <v>0.1832449182658138</v>
+        <v>0.1835192164179104</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5828380389836059</v>
+        <v>0.573731194624487</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1881739876002725</v>
+        <v>0.1897239876002725</v>
       </c>
       <c r="C66">
-        <v>-3.870697804725236</v>
+        <v>-4.349069436953631</v>
       </c>
       <c r="D66">
-        <v>15.79930219527476</v>
+        <v>15.65593056304637</v>
       </c>
       <c r="E66">
-        <v>21.44</v>
+        <v>21.775</v>
       </c>
       <c r="F66">
-        <v>21.44</v>
+        <v>21.775</v>
       </c>
       <c r="G66">
         <v>1.77</v>
@@ -6699,37 +6699,37 @@
         <v>2.47</v>
       </c>
       <c r="M66">
-        <v>4.305152000000001</v>
+        <v>4.372420000000001</v>
       </c>
       <c r="N66">
-        <v>-1.835152000000001</v>
+        <v>-1.902420000000001</v>
       </c>
       <c r="O66">
-        <v>-0.2752728000000001</v>
+        <v>-0.2853630000000001</v>
       </c>
       <c r="P66">
-        <v>-1.559879200000001</v>
+        <v>-1.617057000000001</v>
       </c>
       <c r="Q66">
-        <v>-0.3998792000000007</v>
+        <v>-0.4570570000000009</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1964491363689162</v>
+        <v>0.2007533974080281</v>
       </c>
       <c r="T66">
-        <v>1.963463268207075</v>
+        <v>2.019562218727277</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08605967919367304</v>
+        <v>0.084735684129155</v>
       </c>
       <c r="W66">
-        <v>0.1835192164179104</v>
+        <v>0.1837850746268657</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.573731194624487</v>
+        <v>0.5649045608610332</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1897239876002725</v>
+        <v>0.1912739876002725</v>
       </c>
       <c r="C67">
-        <v>-4.349069436953631</v>
+        <v>-4.82486240199604</v>
       </c>
       <c r="D67">
-        <v>15.65593056304637</v>
+        <v>15.51513759800396</v>
       </c>
       <c r="E67">
-        <v>21.775</v>
+        <v>22.11</v>
       </c>
       <c r="F67">
-        <v>21.775</v>
+        <v>22.11</v>
       </c>
       <c r="G67">
         <v>1.77</v>
@@ -6781,37 +6781,37 @@
         <v>2.47</v>
       </c>
       <c r="M67">
-        <v>4.372420000000001</v>
+        <v>4.439688</v>
       </c>
       <c r="N67">
-        <v>-1.902420000000001</v>
+        <v>-1.969688000000001</v>
       </c>
       <c r="O67">
-        <v>-0.2853630000000001</v>
+        <v>-0.2954532000000001</v>
       </c>
       <c r="P67">
-        <v>-1.617057000000001</v>
+        <v>-1.6742348</v>
       </c>
       <c r="Q67">
-        <v>-0.4570570000000009</v>
+        <v>-0.5142348000000005</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2007533974080281</v>
+        <v>0.2053108502729701</v>
       </c>
       <c r="T67">
-        <v>2.019562218727277</v>
+        <v>2.078961107513373</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.084735684129155</v>
+        <v>0.08345181012719811</v>
       </c>
       <c r="W67">
-        <v>0.1837850746268657</v>
+        <v>0.1840428765264586</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5649045608610332</v>
+        <v>0.5563454008479874</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1912739876002725</v>
+        <v>0.1928239876002725</v>
       </c>
       <c r="C68">
-        <v>-4.82486240199604</v>
+        <v>-5.298145649251698</v>
       </c>
       <c r="D68">
-        <v>15.51513759800396</v>
+        <v>15.3768543507483</v>
       </c>
       <c r="E68">
-        <v>22.11</v>
+        <v>22.445</v>
       </c>
       <c r="F68">
-        <v>22.11</v>
+        <v>22.445</v>
       </c>
       <c r="G68">
         <v>1.77</v>
@@ -6863,37 +6863,37 @@
         <v>2.47</v>
       </c>
       <c r="M68">
-        <v>4.439688</v>
+        <v>4.506956000000001</v>
       </c>
       <c r="N68">
-        <v>-1.969688000000001</v>
+        <v>-2.036956000000001</v>
       </c>
       <c r="O68">
-        <v>-0.2954532000000001</v>
+        <v>-0.3055434000000001</v>
       </c>
       <c r="P68">
-        <v>-1.6742348</v>
+        <v>-1.731412600000001</v>
       </c>
       <c r="Q68">
-        <v>-0.5142348000000005</v>
+        <v>-0.5714126000000008</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2053108502729701</v>
+        <v>0.210144512402454</v>
       </c>
       <c r="T68">
-        <v>2.078961107513373</v>
+        <v>2.141959928953173</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08345181012719811</v>
+        <v>0.08220626072231454</v>
       </c>
       <c r="W68">
-        <v>0.1840428765264586</v>
+        <v>0.1842929828469592</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5563454008479874</v>
+        <v>0.5480417381487637</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1928239876002725</v>
+        <v>0.1943739876002725</v>
       </c>
       <c r="C69">
-        <v>-5.298145649251698</v>
+        <v>-5.768985691707513</v>
       </c>
       <c r="D69">
-        <v>15.3768543507483</v>
+        <v>15.24101430829249</v>
       </c>
       <c r="E69">
-        <v>22.445</v>
+        <v>22.78</v>
       </c>
       <c r="F69">
-        <v>22.445</v>
+        <v>22.78</v>
       </c>
       <c r="G69">
         <v>1.77</v>
@@ -6945,37 +6945,37 @@
         <v>2.47</v>
       </c>
       <c r="M69">
-        <v>4.506956000000001</v>
+        <v>4.574224</v>
       </c>
       <c r="N69">
-        <v>-2.036956000000001</v>
+        <v>-2.104224</v>
       </c>
       <c r="O69">
-        <v>-0.3055434000000001</v>
+        <v>-0.3156336</v>
       </c>
       <c r="P69">
-        <v>-1.731412600000001</v>
+        <v>-1.7885904</v>
       </c>
       <c r="Q69">
-        <v>-0.5714126000000008</v>
+        <v>-0.6285904000000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.210144512402454</v>
+        <v>0.2152802784150307</v>
       </c>
       <c r="T69">
-        <v>2.141959928953173</v>
+        <v>2.208896176732959</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08220626072231454</v>
+        <v>0.08099734512345699</v>
       </c>
       <c r="W69">
-        <v>0.1842929828469592</v>
+        <v>0.1845357330992098</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5480417381487637</v>
+        <v>0.5399823008230467</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1943739876002725</v>
+        <v>0.1959239876002725</v>
       </c>
       <c r="C70">
-        <v>-5.768985691707513</v>
+        <v>-6.237446712612758</v>
       </c>
       <c r="D70">
-        <v>15.24101430829249</v>
+        <v>15.10755328738724</v>
       </c>
       <c r="E70">
-        <v>22.78</v>
+        <v>23.115</v>
       </c>
       <c r="F70">
-        <v>22.78</v>
+        <v>23.115</v>
       </c>
       <c r="G70">
         <v>1.77</v>
@@ -7027,37 +7027,37 @@
         <v>2.47</v>
       </c>
       <c r="M70">
-        <v>4.574224</v>
+        <v>4.641492</v>
       </c>
       <c r="N70">
-        <v>-2.104224</v>
+        <v>-2.171492000000001</v>
       </c>
       <c r="O70">
-        <v>-0.3156336</v>
+        <v>-0.3257238000000001</v>
       </c>
       <c r="P70">
-        <v>-1.7885904</v>
+        <v>-1.845768200000001</v>
       </c>
       <c r="Q70">
-        <v>-0.6285904000000004</v>
+        <v>-0.6857682000000007</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2152802784150307</v>
+        <v>0.2207473841703543</v>
       </c>
       <c r="T70">
-        <v>2.208896176732959</v>
+        <v>2.280150892111442</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08099734512345699</v>
+        <v>0.07982347055645035</v>
       </c>
       <c r="W70">
-        <v>0.1845357330992098</v>
+        <v>0.1847714471122648</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5399823008230467</v>
+        <v>0.5321564703763357</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1959239876002725</v>
+        <v>0.1974739876002725</v>
       </c>
       <c r="C71">
-        <v>-6.237446712612758</v>
+        <v>-6.703590666597712</v>
       </c>
       <c r="D71">
-        <v>15.10755328738724</v>
+        <v>14.97640933340229</v>
       </c>
       <c r="E71">
-        <v>23.115</v>
+        <v>23.45</v>
       </c>
       <c r="F71">
-        <v>23.115</v>
+        <v>23.45</v>
       </c>
       <c r="G71">
         <v>1.77</v>
@@ -7109,37 +7109,37 @@
         <v>2.47</v>
       </c>
       <c r="M71">
-        <v>4.641492</v>
+        <v>4.708760000000001</v>
       </c>
       <c r="N71">
-        <v>-2.171492000000001</v>
+        <v>-2.238760000000001</v>
       </c>
       <c r="O71">
-        <v>-0.3257238000000001</v>
+        <v>-0.3358140000000001</v>
       </c>
       <c r="P71">
-        <v>-1.845768200000001</v>
+        <v>-1.902946000000001</v>
       </c>
       <c r="Q71">
-        <v>-0.6857682000000007</v>
+        <v>-0.742946000000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2207473841703543</v>
+        <v>0.2265789636426994</v>
       </c>
       <c r="T71">
-        <v>2.280150892111442</v>
+        <v>2.35615592184849</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.07982347055645035</v>
+        <v>0.07868313526278678</v>
       </c>
       <c r="W71">
-        <v>0.1847714471122648</v>
+        <v>0.1850004264392324</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5321564703763357</v>
+        <v>0.5245542350852452</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1974739876002725</v>
+        <v>0.1990239876002725</v>
       </c>
       <c r="C72">
-        <v>-6.703590666597712</v>
+        <v>-7.167477375570918</v>
       </c>
       <c r="D72">
-        <v>14.97640933340229</v>
+        <v>14.84752262442908</v>
       </c>
       <c r="E72">
-        <v>23.45</v>
+        <v>23.785</v>
       </c>
       <c r="F72">
-        <v>23.45</v>
+        <v>23.785</v>
       </c>
       <c r="G72">
         <v>1.77</v>
@@ -7191,37 +7191,37 @@
         <v>2.47</v>
       </c>
       <c r="M72">
-        <v>4.708760000000001</v>
+        <v>4.776028000000001</v>
       </c>
       <c r="N72">
-        <v>-2.238760000000001</v>
+        <v>-2.306028000000001</v>
       </c>
       <c r="O72">
-        <v>-0.3358140000000001</v>
+        <v>-0.3459042000000002</v>
       </c>
       <c r="P72">
-        <v>-1.902946000000001</v>
+        <v>-1.960123800000001</v>
       </c>
       <c r="Q72">
-        <v>-0.742946000000001</v>
+        <v>-0.8001238000000013</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2265789636426994</v>
+        <v>0.2328127210096891</v>
       </c>
       <c r="T72">
-        <v>2.35615592184849</v>
+        <v>2.4374026777743</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.07868313526278678</v>
+        <v>0.07757492209007147</v>
       </c>
       <c r="W72">
-        <v>0.1850004264392324</v>
+        <v>0.1852229556443137</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5245542350852452</v>
+        <v>0.5171661472671432</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1990239876002725</v>
+        <v>0.2005739876002725</v>
       </c>
       <c r="C73">
-        <v>-7.167477375570915</v>
+        <v>-7.629164619706973</v>
       </c>
       <c r="D73">
-        <v>14.84752262442908</v>
+        <v>14.72083538029302</v>
       </c>
       <c r="E73">
-        <v>23.785</v>
+        <v>24.12</v>
       </c>
       <c r="F73">
-        <v>23.785</v>
+        <v>24.12</v>
       </c>
       <c r="G73">
         <v>1.77</v>
@@ -7273,37 +7273,37 @@
         <v>2.47</v>
       </c>
       <c r="M73">
-        <v>4.776028</v>
+        <v>4.843296</v>
       </c>
       <c r="N73">
-        <v>-2.306028</v>
+        <v>-2.373296</v>
       </c>
       <c r="O73">
-        <v>-0.3459042000000001</v>
+        <v>-0.3559944</v>
       </c>
       <c r="P73">
-        <v>-1.9601238</v>
+        <v>-2.0173016</v>
       </c>
       <c r="Q73">
-        <v>-0.8001238000000004</v>
+        <v>-0.8573015999999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2328127210096891</v>
+        <v>0.2394917467600351</v>
       </c>
       <c r="T73">
-        <v>2.437402677774299</v>
+        <v>2.524452773409096</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.07757492209007148</v>
+        <v>0.07649749261659827</v>
       </c>
       <c r="W73">
-        <v>0.1852229556443137</v>
+        <v>0.1854393034825871</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5171661472671433</v>
+        <v>0.5099832841106552</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2005739876002725</v>
+        <v>0.2021239876002725</v>
       </c>
       <c r="C74">
-        <v>-7.629164619706973</v>
+        <v>-8.088708223815591</v>
       </c>
       <c r="D74">
-        <v>14.72083538029302</v>
+        <v>14.59629177618441</v>
       </c>
       <c r="E74">
-        <v>24.12</v>
+        <v>24.455</v>
       </c>
       <c r="F74">
-        <v>24.12</v>
+        <v>24.455</v>
       </c>
       <c r="G74">
         <v>1.77</v>
@@ -7355,37 +7355,37 @@
         <v>2.47</v>
       </c>
       <c r="M74">
-        <v>4.843296</v>
+        <v>4.910564</v>
       </c>
       <c r="N74">
-        <v>-2.373296</v>
+        <v>-2.440564</v>
       </c>
       <c r="O74">
-        <v>-0.3559944</v>
+        <v>-0.3660846</v>
       </c>
       <c r="P74">
-        <v>-2.0173016</v>
+        <v>-2.0744794</v>
       </c>
       <c r="Q74">
-        <v>-0.8573015999999998</v>
+        <v>-0.9144794000000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2394917467600351</v>
+        <v>0.2466655151585549</v>
       </c>
       <c r="T74">
-        <v>2.524452773409096</v>
+        <v>2.617951024276099</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07649749261659827</v>
+        <v>0.07544958175883666</v>
       </c>
       <c r="W74">
-        <v>0.1854393034825871</v>
+        <v>0.1856497239828256</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5099832841106552</v>
+        <v>0.5029972117255777</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2021239876002725</v>
+        <v>0.2300432083579589</v>
       </c>
       <c r="C75">
-        <v>-8.088708223815591</v>
+        <v>-10.35391164496731</v>
       </c>
       <c r="D75">
-        <v>14.59629177618441</v>
+        <v>12.66608835503269</v>
       </c>
       <c r="E75">
-        <v>24.455</v>
+        <v>24.79</v>
       </c>
       <c r="F75">
-        <v>24.455</v>
+        <v>24.79</v>
       </c>
       <c r="G75">
         <v>1.77</v>
@@ -7437,45 +7437,45 @@
         <v>2.47</v>
       </c>
       <c r="M75">
-        <v>4.910564</v>
+        <v>5.845482</v>
       </c>
       <c r="N75">
-        <v>-2.440564</v>
+        <v>-3.375482</v>
       </c>
       <c r="O75">
-        <v>-0.3660846</v>
+        <v>-0.5063223</v>
       </c>
       <c r="P75">
-        <v>-2.0744794</v>
+        <v>-2.8691597</v>
       </c>
       <c r="Q75">
-        <v>-0.9144794000000001</v>
+        <v>-1.7091597</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2466655151585549</v>
+        <v>0.2561958071172933</v>
       </c>
       <c r="T75">
-        <v>2.617951024276099</v>
+        <v>2.742162676910127</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07544958175883666</v>
+        <v>0.06338228395879072</v>
       </c>
       <c r="W75">
-        <v>0.1856497239828256</v>
+        <v>0.2208544574425171</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5029972117255777</v>
+        <v>0.4225485597252716</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2300432083579589</v>
+        <v>0.231943208357959</v>
       </c>
       <c r="C76">
-        <v>-10.35391164496731</v>
+        <v>-10.8018814768397</v>
       </c>
       <c r="D76">
-        <v>12.66608835503269</v>
+        <v>12.5531185231603</v>
       </c>
       <c r="E76">
-        <v>24.79</v>
+        <v>25.125</v>
       </c>
       <c r="F76">
-        <v>24.79</v>
+        <v>25.125</v>
       </c>
       <c r="G76">
         <v>1.77</v>
@@ -7519,37 +7519,37 @@
         <v>2.47</v>
       </c>
       <c r="M76">
-        <v>5.845482</v>
+        <v>5.924475</v>
       </c>
       <c r="N76">
-        <v>-3.375482</v>
+        <v>-3.454475</v>
       </c>
       <c r="O76">
-        <v>-0.5063223</v>
+        <v>-0.5181712500000001</v>
       </c>
       <c r="P76">
-        <v>-2.8691597</v>
+        <v>-2.93630375</v>
       </c>
       <c r="Q76">
-        <v>-1.7091597</v>
+        <v>-1.776303750000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2561958071172933</v>
+        <v>0.2646116394019851</v>
       </c>
       <c r="T76">
-        <v>2.742162676910127</v>
+        <v>2.851849183986533</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06338228395879072</v>
+        <v>0.06253718683934019</v>
       </c>
       <c r="W76">
-        <v>0.2208544574425171</v>
+        <v>0.2210537313432836</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4225485597252716</v>
+        <v>0.4169145789289346</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.231943208357959</v>
+        <v>0.233843208357959</v>
       </c>
       <c r="C77">
-        <v>-10.8018814768397</v>
+        <v>-11.24785394979461</v>
       </c>
       <c r="D77">
-        <v>12.5531185231603</v>
+        <v>12.44214605020539</v>
       </c>
       <c r="E77">
-        <v>25.125</v>
+        <v>25.46</v>
       </c>
       <c r="F77">
-        <v>25.125</v>
+        <v>25.46</v>
       </c>
       <c r="G77">
         <v>1.77</v>
@@ -7601,37 +7601,37 @@
         <v>2.47</v>
       </c>
       <c r="M77">
-        <v>5.924475</v>
+        <v>6.003468000000001</v>
       </c>
       <c r="N77">
-        <v>-3.454475</v>
+        <v>-3.533468000000001</v>
       </c>
       <c r="O77">
-        <v>-0.5181712500000001</v>
+        <v>-0.5300202000000002</v>
       </c>
       <c r="P77">
-        <v>-2.93630375</v>
+        <v>-3.003447800000001</v>
       </c>
       <c r="Q77">
-        <v>-1.776303750000001</v>
+        <v>-1.843447800000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2646116394019851</v>
+        <v>0.2737287910437344</v>
       </c>
       <c r="T77">
-        <v>2.851849183986533</v>
+        <v>2.970676233319305</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06253718683934019</v>
+        <v>0.06171432911776991</v>
       </c>
       <c r="W77">
-        <v>0.2210537313432836</v>
+        <v>0.2212477611940299</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4169145789289346</v>
+        <v>0.4114288607851327</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.233843208357959</v>
+        <v>0.2357432083579589</v>
       </c>
       <c r="C78">
-        <v>-11.24785394979461</v>
+        <v>-11.69188157100177</v>
       </c>
       <c r="D78">
-        <v>12.44214605020539</v>
+        <v>12.33311842899823</v>
       </c>
       <c r="E78">
-        <v>25.46</v>
+        <v>25.795</v>
       </c>
       <c r="F78">
-        <v>25.46</v>
+        <v>25.795</v>
       </c>
       <c r="G78">
         <v>1.77</v>
@@ -7683,37 +7683,37 @@
         <v>2.47</v>
       </c>
       <c r="M78">
-        <v>6.003468000000001</v>
+        <v>6.082461</v>
       </c>
       <c r="N78">
-        <v>-3.533468000000001</v>
+        <v>-3.612461000000001</v>
       </c>
       <c r="O78">
-        <v>-0.5300202000000002</v>
+        <v>-0.54186915</v>
       </c>
       <c r="P78">
-        <v>-3.003447800000001</v>
+        <v>-3.07059185</v>
       </c>
       <c r="Q78">
-        <v>-1.843447800000001</v>
+        <v>-1.910591850000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2737287910437344</v>
+        <v>0.2836387384804185</v>
       </c>
       <c r="T78">
-        <v>2.970676233319305</v>
+        <v>3.099836069550578</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06171432911776991</v>
+        <v>0.06091284432403264</v>
       </c>
       <c r="W78">
-        <v>0.2212477611940299</v>
+        <v>0.2214367513083931</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4114288607851327</v>
+        <v>0.4060856288268844</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2357432083579589</v>
+        <v>0.2376432083579589</v>
       </c>
       <c r="C79">
-        <v>-11.69188157100177</v>
+        <v>-12.13401502318582</v>
       </c>
       <c r="D79">
-        <v>12.33311842899823</v>
+        <v>12.22598497681419</v>
       </c>
       <c r="E79">
-        <v>25.795</v>
+        <v>26.13</v>
       </c>
       <c r="F79">
-        <v>25.795</v>
+        <v>26.13</v>
       </c>
       <c r="G79">
         <v>1.77</v>
@@ -7765,37 +7765,37 @@
         <v>2.47</v>
       </c>
       <c r="M79">
-        <v>6.082461</v>
+        <v>6.161454000000001</v>
       </c>
       <c r="N79">
-        <v>-3.612461000000001</v>
+        <v>-3.691454000000001</v>
       </c>
       <c r="O79">
-        <v>-0.54186915</v>
+        <v>-0.5537181000000001</v>
       </c>
       <c r="P79">
-        <v>-3.07059185</v>
+        <v>-3.137735900000001</v>
       </c>
       <c r="Q79">
-        <v>-1.910591850000001</v>
+        <v>-1.977735900000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2836387384804185</v>
+        <v>0.2944495902295284</v>
       </c>
       <c r="T79">
-        <v>3.099836069550578</v>
+        <v>3.240737709075605</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06091284432403264</v>
+        <v>0.06013191042244248</v>
       </c>
       <c r="W79">
-        <v>0.2214367513083931</v>
+        <v>0.2216208955223881</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4060856288268844</v>
+        <v>0.4008794028162832</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2376432083579589</v>
+        <v>0.239543208357959</v>
       </c>
       <c r="C80">
-        <v>-12.13401502318582</v>
+        <v>-12.57430324318542</v>
       </c>
       <c r="D80">
-        <v>12.22598497681419</v>
+        <v>12.12069675681458</v>
       </c>
       <c r="E80">
-        <v>26.13</v>
+        <v>26.465</v>
       </c>
       <c r="F80">
-        <v>26.13</v>
+        <v>26.465</v>
       </c>
       <c r="G80">
         <v>1.77</v>
@@ -7847,37 +7847,37 @@
         <v>2.47</v>
       </c>
       <c r="M80">
-        <v>6.161454000000001</v>
+        <v>6.240447000000001</v>
       </c>
       <c r="N80">
-        <v>-3.691454000000001</v>
+        <v>-3.770447000000001</v>
       </c>
       <c r="O80">
-        <v>-0.5537181000000001</v>
+        <v>-0.5655670500000001</v>
       </c>
       <c r="P80">
-        <v>-3.137735900000001</v>
+        <v>-3.20487995</v>
       </c>
       <c r="Q80">
-        <v>-1.977735900000001</v>
+        <v>-2.04487995</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2944495902295284</v>
+        <v>0.3062900469071251</v>
       </c>
       <c r="T80">
-        <v>3.240737709075605</v>
+        <v>3.395058552364921</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06013191042244248</v>
+        <v>0.05937074699937359</v>
       </c>
       <c r="W80">
-        <v>0.2216208955223881</v>
+        <v>0.2218003778575477</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4008794028162832</v>
+        <v>0.395804979995824</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.239543208357959</v>
+        <v>0.241443208357959</v>
       </c>
       <c r="C81">
-        <v>-12.57430324318542</v>
+        <v>-13.01279349648786</v>
       </c>
       <c r="D81">
-        <v>12.12069675681458</v>
+        <v>12.01720650351214</v>
       </c>
       <c r="E81">
-        <v>26.465</v>
+        <v>26.8</v>
       </c>
       <c r="F81">
-        <v>26.465</v>
+        <v>26.8</v>
       </c>
       <c r="G81">
         <v>1.77</v>
@@ -7929,37 +7929,37 @@
         <v>2.47</v>
       </c>
       <c r="M81">
-        <v>6.240447000000001</v>
+        <v>6.31944</v>
       </c>
       <c r="N81">
-        <v>-3.770447000000001</v>
+        <v>-3.84944</v>
       </c>
       <c r="O81">
-        <v>-0.5655670500000001</v>
+        <v>-0.577416</v>
       </c>
       <c r="P81">
-        <v>-3.20487995</v>
+        <v>-3.272024</v>
       </c>
       <c r="Q81">
-        <v>-2.04487995</v>
+        <v>-2.112024000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3062900469071251</v>
+        <v>0.3193145492524813</v>
       </c>
       <c r="T81">
-        <v>3.395058552364921</v>
+        <v>3.564811479983166</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05937074699937359</v>
+        <v>0.05862861266188142</v>
       </c>
       <c r="W81">
-        <v>0.2218003778575477</v>
+        <v>0.2219753731343284</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.395804979995824</v>
+        <v>0.3908574177458761</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.241443208357959</v>
+        <v>0.243343208357959</v>
       </c>
       <c r="C82">
-        <v>-13.01279349648786</v>
+        <v>-13.44953144797756</v>
       </c>
       <c r="D82">
-        <v>12.01720650351214</v>
+        <v>11.91546855202244</v>
       </c>
       <c r="E82">
-        <v>26.8</v>
+        <v>27.135</v>
       </c>
       <c r="F82">
-        <v>26.8</v>
+        <v>27.135</v>
       </c>
       <c r="G82">
         <v>1.77</v>
@@ -8011,37 +8011,37 @@
         <v>2.47</v>
       </c>
       <c r="M82">
-        <v>6.31944</v>
+        <v>6.398433000000001</v>
       </c>
       <c r="N82">
-        <v>-3.84944</v>
+        <v>-3.928433000000001</v>
       </c>
       <c r="O82">
-        <v>-0.577416</v>
+        <v>-0.5892649500000001</v>
       </c>
       <c r="P82">
-        <v>-3.272024</v>
+        <v>-3.339168050000001</v>
       </c>
       <c r="Q82">
-        <v>-2.112024000000001</v>
+        <v>-2.179168050000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3193145492524813</v>
+        <v>0.3337100518447172</v>
       </c>
       <c r="T82">
-        <v>3.564811479983166</v>
+        <v>3.752433136824386</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05862861266188142</v>
+        <v>0.05790480262901868</v>
       </c>
       <c r="W82">
-        <v>0.2219753731343284</v>
+        <v>0.2221460475400774</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3908574177458761</v>
+        <v>0.3860320175267913</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.243343208357959</v>
+        <v>0.2452432083579589</v>
       </c>
       <c r="C83">
-        <v>-13.44953144797756</v>
+        <v>-13.88456122912094</v>
       </c>
       <c r="D83">
-        <v>11.91546855202244</v>
+        <v>11.81543877087906</v>
       </c>
       <c r="E83">
-        <v>27.135</v>
+        <v>27.47</v>
       </c>
       <c r="F83">
-        <v>27.135</v>
+        <v>27.47</v>
       </c>
       <c r="G83">
         <v>1.77</v>
@@ -8093,37 +8093,37 @@
         <v>2.47</v>
       </c>
       <c r="M83">
-        <v>6.398433000000001</v>
+        <v>6.477426000000001</v>
       </c>
       <c r="N83">
-        <v>-3.928433000000001</v>
+        <v>-4.007426000000001</v>
       </c>
       <c r="O83">
-        <v>-0.5892649500000001</v>
+        <v>-0.6011139000000002</v>
       </c>
       <c r="P83">
-        <v>-3.339168050000001</v>
+        <v>-3.406312100000001</v>
       </c>
       <c r="Q83">
-        <v>-2.179168050000001</v>
+        <v>-2.246312100000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3337100518447172</v>
+        <v>0.3497050547249793</v>
       </c>
       <c r="T83">
-        <v>3.752433136824386</v>
+        <v>3.960901644425741</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05790480262901868</v>
+        <v>0.0571986464993965</v>
       </c>
       <c r="W83">
-        <v>0.2221460475400774</v>
+        <v>0.2223125591554423</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3860320175267913</v>
+        <v>0.3813243099959767</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2452432083579589</v>
+        <v>0.247143208357959</v>
       </c>
       <c r="C84">
-        <v>-13.88456122912094</v>
+        <v>-14.3179255017955</v>
       </c>
       <c r="D84">
-        <v>11.81543877087906</v>
+        <v>11.71707449820451</v>
       </c>
       <c r="E84">
-        <v>27.47</v>
+        <v>27.805</v>
       </c>
       <c r="F84">
-        <v>27.47</v>
+        <v>27.805</v>
       </c>
       <c r="G84">
         <v>1.77</v>
@@ -8175,37 +8175,37 @@
         <v>2.47</v>
       </c>
       <c r="M84">
-        <v>6.477426000000001</v>
+        <v>6.556419000000001</v>
       </c>
       <c r="N84">
-        <v>-4.007426000000001</v>
+        <v>-4.086419000000001</v>
       </c>
       <c r="O84">
-        <v>-0.6011139000000002</v>
+        <v>-0.6129628500000002</v>
       </c>
       <c r="P84">
-        <v>-3.406312100000001</v>
+        <v>-3.473456150000001</v>
       </c>
       <c r="Q84">
-        <v>-2.246312100000002</v>
+        <v>-2.313456150000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3497050547249793</v>
+        <v>0.3675818226499781</v>
       </c>
       <c r="T84">
-        <v>3.960901644425741</v>
+        <v>4.193895858803725</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0571986464993965</v>
+        <v>0.05650950618012666</v>
       </c>
       <c r="W84">
-        <v>0.2223125591554423</v>
+        <v>0.2224750584427262</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3813243099959767</v>
+        <v>0.3767300412008444</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.247143208357959</v>
+        <v>0.249043208357959</v>
       </c>
       <c r="C85">
-        <v>-14.3179255017955</v>
+        <v>-14.74966551895677</v>
       </c>
       <c r="D85">
-        <v>11.71707449820451</v>
+        <v>11.62033448104324</v>
       </c>
       <c r="E85">
-        <v>27.805</v>
+        <v>28.14</v>
       </c>
       <c r="F85">
-        <v>27.805</v>
+        <v>28.14</v>
       </c>
       <c r="G85">
         <v>1.77</v>
@@ -8257,37 +8257,37 @@
         <v>2.47</v>
       </c>
       <c r="M85">
-        <v>6.556419000000001</v>
+        <v>6.635412000000001</v>
       </c>
       <c r="N85">
-        <v>-4.086419000000001</v>
+        <v>-4.165412000000002</v>
       </c>
       <c r="O85">
-        <v>-0.6129628500000002</v>
+        <v>-0.6248118000000003</v>
       </c>
       <c r="P85">
-        <v>-3.473456150000001</v>
+        <v>-3.540600200000001</v>
       </c>
       <c r="Q85">
-        <v>-2.313456150000001</v>
+        <v>-2.380600200000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3675818226499781</v>
+        <v>0.3876931865656018</v>
       </c>
       <c r="T85">
-        <v>4.193895858803725</v>
+        <v>4.456014349978959</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05650950618012666</v>
+        <v>0.05583677396369658</v>
       </c>
       <c r="W85">
-        <v>0.2224750584427262</v>
+        <v>0.2226336886993603</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3767300412008444</v>
+        <v>0.3722451597579772</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.249043208357959</v>
+        <v>0.250943208357959</v>
       </c>
       <c r="C86">
-        <v>-14.74966551895676</v>
+        <v>-15.17982118232474</v>
       </c>
       <c r="D86">
-        <v>11.62033448104324</v>
+        <v>11.52517881767526</v>
       </c>
       <c r="E86">
-        <v>28.14</v>
+        <v>28.475</v>
       </c>
       <c r="F86">
-        <v>28.14</v>
+        <v>28.475</v>
       </c>
       <c r="G86">
         <v>1.77</v>
@@ -8339,37 +8339,37 @@
         <v>2.47</v>
       </c>
       <c r="M86">
-        <v>6.635412000000001</v>
+        <v>6.714405</v>
       </c>
       <c r="N86">
-        <v>-4.165412000000001</v>
+        <v>-4.244405</v>
       </c>
       <c r="O86">
-        <v>-0.6248118000000001</v>
+        <v>-0.63666075</v>
       </c>
       <c r="P86">
-        <v>-3.540600200000001</v>
+        <v>-3.607744250000001</v>
       </c>
       <c r="Q86">
-        <v>-2.380600200000001</v>
+        <v>-2.44774425</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3876931865656016</v>
+        <v>0.410486065669975</v>
       </c>
       <c r="T86">
-        <v>4.456014349978957</v>
+        <v>4.753081973310887</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05583677396369659</v>
+        <v>0.05517987074059428</v>
       </c>
       <c r="W86">
-        <v>0.2226336886993603</v>
+        <v>0.2227885864793679</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3722451597579772</v>
+        <v>0.3678658049372953</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.250943208357959</v>
+        <v>0.2528432083579589</v>
       </c>
       <c r="C87">
-        <v>-15.17982118232474</v>
+        <v>-15.6084310972589</v>
       </c>
       <c r="D87">
-        <v>11.52517881767526</v>
+        <v>11.43156890274109</v>
       </c>
       <c r="E87">
-        <v>28.475</v>
+        <v>28.81</v>
       </c>
       <c r="F87">
-        <v>28.475</v>
+        <v>28.81</v>
       </c>
       <c r="G87">
         <v>1.77</v>
@@ -8421,37 +8421,37 @@
         <v>2.47</v>
       </c>
       <c r="M87">
-        <v>6.714405</v>
+        <v>6.793398</v>
       </c>
       <c r="N87">
-        <v>-4.244405</v>
+        <v>-4.323398</v>
       </c>
       <c r="O87">
-        <v>-0.63666075</v>
+        <v>-0.6485097</v>
       </c>
       <c r="P87">
-        <v>-3.607744250000001</v>
+        <v>-3.6748883</v>
       </c>
       <c r="Q87">
-        <v>-2.44774425</v>
+        <v>-2.5148883</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.410486065669975</v>
+        <v>0.4365350703606876</v>
       </c>
       <c r="T87">
-        <v>4.753081973310887</v>
+        <v>5.092587828547379</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05517987074059428</v>
+        <v>0.05453824433663388</v>
       </c>
       <c r="W87">
-        <v>0.2227885864793679</v>
+        <v>0.2229398819854217</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3678658049372953</v>
+        <v>0.3635882955775592</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2528432083579589</v>
+        <v>0.2547432083579589</v>
       </c>
       <c r="C88">
-        <v>-15.6084310972589</v>
+        <v>-16.03553262498066</v>
       </c>
       <c r="D88">
-        <v>11.43156890274109</v>
+        <v>11.33946737501934</v>
       </c>
       <c r="E88">
-        <v>28.81</v>
+        <v>29.145</v>
       </c>
       <c r="F88">
-        <v>28.81</v>
+        <v>29.145</v>
       </c>
       <c r="G88">
         <v>1.77</v>
@@ -8503,37 +8503,37 @@
         <v>2.47</v>
       </c>
       <c r="M88">
-        <v>6.793398</v>
+        <v>6.872391</v>
       </c>
       <c r="N88">
-        <v>-4.323398</v>
+        <v>-4.402391000000001</v>
       </c>
       <c r="O88">
-        <v>-0.6485097</v>
+        <v>-0.66035865</v>
       </c>
       <c r="P88">
-        <v>-3.6748883</v>
+        <v>-3.742032350000001</v>
       </c>
       <c r="Q88">
-        <v>-2.5148883</v>
+        <v>-2.58203235</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4365350703606876</v>
+        <v>0.4665916142345866</v>
       </c>
       <c r="T88">
-        <v>5.092587828547379</v>
+        <v>5.484325353820254</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05453824433663388</v>
+        <v>0.05391136796494844</v>
       </c>
       <c r="W88">
-        <v>0.2229398819854217</v>
+        <v>0.2230876994338652</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3635882955775592</v>
+        <v>0.3594091197663229</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2547432083579589</v>
+        <v>0.256643208357959</v>
       </c>
       <c r="C89">
-        <v>-16.03553262498066</v>
+        <v>-16.46116193229142</v>
       </c>
       <c r="D89">
-        <v>11.33946737501934</v>
+        <v>11.24883806770858</v>
       </c>
       <c r="E89">
-        <v>29.145</v>
+        <v>29.48</v>
       </c>
       <c r="F89">
-        <v>29.145</v>
+        <v>29.48</v>
       </c>
       <c r="G89">
         <v>1.77</v>
@@ -8585,37 +8585,37 @@
         <v>2.47</v>
       </c>
       <c r="M89">
-        <v>6.872391</v>
+        <v>6.951384</v>
       </c>
       <c r="N89">
-        <v>-4.402391000000001</v>
+        <v>-4.481384</v>
       </c>
       <c r="O89">
-        <v>-0.66035865</v>
+        <v>-0.6722076</v>
       </c>
       <c r="P89">
-        <v>-3.742032350000001</v>
+        <v>-3.8091764</v>
       </c>
       <c r="Q89">
-        <v>-2.58203235</v>
+        <v>-2.6491764</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4665916142345866</v>
+        <v>0.5016575820874688</v>
       </c>
       <c r="T89">
-        <v>5.484325353820254</v>
+        <v>5.94135246663861</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05391136796494844</v>
+        <v>0.05329873878352857</v>
       </c>
       <c r="W89">
-        <v>0.2230876994338652</v>
+        <v>0.223232157394844</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3594091197663229</v>
+        <v>0.3553249252235238</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.256643208357959</v>
+        <v>0.258543208357959</v>
       </c>
       <c r="C90">
-        <v>-16.46116193229142</v>
+        <v>-16.88535403892542</v>
       </c>
       <c r="D90">
-        <v>11.24883806770858</v>
+        <v>11.15964596107458</v>
       </c>
       <c r="E90">
-        <v>29.48</v>
+        <v>29.815</v>
       </c>
       <c r="F90">
-        <v>29.48</v>
+        <v>29.815</v>
       </c>
       <c r="G90">
         <v>1.77</v>
@@ -8667,37 +8667,37 @@
         <v>2.47</v>
       </c>
       <c r="M90">
-        <v>6.951384</v>
+        <v>7.030377000000001</v>
       </c>
       <c r="N90">
-        <v>-4.481384</v>
+        <v>-4.560377000000001</v>
       </c>
       <c r="O90">
-        <v>-0.6722076</v>
+        <v>-0.6840565500000001</v>
       </c>
       <c r="P90">
-        <v>-3.8091764</v>
+        <v>-3.876320450000001</v>
       </c>
       <c r="Q90">
-        <v>-2.6491764</v>
+        <v>-2.71632045</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5016575820874688</v>
+        <v>0.5430991804590569</v>
       </c>
       <c r="T90">
-        <v>5.94135246663861</v>
+        <v>6.48147541815121</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05329873878352857</v>
+        <v>0.05269987655000577</v>
       </c>
       <c r="W90">
-        <v>0.223232157394844</v>
+        <v>0.2233733691095087</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3553249252235238</v>
+        <v>0.3513325103333719</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.258543208357959</v>
+        <v>0.260443208357959</v>
       </c>
       <c r="C91">
-        <v>-16.88535403892542</v>
+        <v>-17.30814286266751</v>
       </c>
       <c r="D91">
-        <v>11.15964596107458</v>
+        <v>11.07185713733249</v>
       </c>
       <c r="E91">
-        <v>29.815</v>
+        <v>30.15</v>
       </c>
       <c r="F91">
-        <v>29.815</v>
+        <v>30.15</v>
       </c>
       <c r="G91">
         <v>1.77</v>
@@ -8749,37 +8749,37 @@
         <v>2.47</v>
       </c>
       <c r="M91">
-        <v>7.030377000000001</v>
+        <v>7.109370000000001</v>
       </c>
       <c r="N91">
-        <v>-4.560377000000001</v>
+        <v>-4.639370000000001</v>
       </c>
       <c r="O91">
-        <v>-0.6840565500000001</v>
+        <v>-0.6959055000000002</v>
       </c>
       <c r="P91">
-        <v>-3.876320450000001</v>
+        <v>-3.943464500000001</v>
       </c>
       <c r="Q91">
-        <v>-2.71632045</v>
+        <v>-2.783464500000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5430991804590569</v>
+        <v>0.5928290985049627</v>
       </c>
       <c r="T91">
-        <v>6.48147541815121</v>
+        <v>7.129622959966333</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05269987655000577</v>
+        <v>0.05211432236611682</v>
       </c>
       <c r="W91">
-        <v>0.2233733691095087</v>
+        <v>0.2235114427860697</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3513325103333719</v>
+        <v>0.3474288157741121</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.260443208357959</v>
+        <v>0.262343208357959</v>
       </c>
       <c r="C92">
-        <v>-17.30814286266751</v>
+        <v>-17.72956126235799</v>
       </c>
       <c r="D92">
-        <v>11.07185713733249</v>
+        <v>10.98543873764201</v>
       </c>
       <c r="E92">
-        <v>30.15</v>
+        <v>30.485</v>
       </c>
       <c r="F92">
-        <v>30.15</v>
+        <v>30.485</v>
       </c>
       <c r="G92">
         <v>1.77</v>
@@ -8831,37 +8831,37 @@
         <v>2.47</v>
       </c>
       <c r="M92">
-        <v>7.109370000000001</v>
+        <v>7.188363</v>
       </c>
       <c r="N92">
-        <v>-4.639370000000001</v>
+        <v>-4.718363</v>
       </c>
       <c r="O92">
-        <v>-0.6959055000000002</v>
+        <v>-0.70775445</v>
       </c>
       <c r="P92">
-        <v>-3.943464500000001</v>
+        <v>-4.01060855</v>
       </c>
       <c r="Q92">
-        <v>-2.783464500000001</v>
+        <v>-2.85060855</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5928290985049627</v>
+        <v>0.6536101094499586</v>
       </c>
       <c r="T92">
-        <v>7.129622959966333</v>
+        <v>7.921803288851481</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05211432236611682</v>
+        <v>0.0515416375049507</v>
       </c>
       <c r="W92">
-        <v>0.2235114427860697</v>
+        <v>0.2236464818763327</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3474288157741121</v>
+        <v>0.3436109166996714</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.262343208357959</v>
+        <v>0.2642432083579589</v>
       </c>
       <c r="C93">
-        <v>-17.72956126235799</v>
+        <v>-18.14964107889907</v>
       </c>
       <c r="D93">
-        <v>10.98543873764201</v>
+        <v>10.90035892110093</v>
       </c>
       <c r="E93">
-        <v>30.485</v>
+        <v>30.82</v>
       </c>
       <c r="F93">
-        <v>30.485</v>
+        <v>30.82</v>
       </c>
       <c r="G93">
         <v>1.77</v>
@@ -8913,37 +8913,37 @@
         <v>2.47</v>
       </c>
       <c r="M93">
-        <v>7.188363</v>
+        <v>7.267356</v>
       </c>
       <c r="N93">
-        <v>-4.718363</v>
+        <v>-4.797356000000001</v>
       </c>
       <c r="O93">
-        <v>-0.70775445</v>
+        <v>-0.7196034000000001</v>
       </c>
       <c r="P93">
-        <v>-4.01060855</v>
+        <v>-4.0777526</v>
       </c>
       <c r="Q93">
-        <v>-2.85060855</v>
+        <v>-2.9177526</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6536101094499586</v>
+        <v>0.7295863731312036</v>
       </c>
       <c r="T93">
-        <v>7.921803288851481</v>
+        <v>8.912028699957919</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0515416375049507</v>
+        <v>0.0509814023146795</v>
       </c>
       <c r="W93">
-        <v>0.2236464818763327</v>
+        <v>0.2237785853341986</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3436109166996714</v>
+        <v>0.3398760154311966</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2642432083579589</v>
+        <v>0.266143208357959</v>
       </c>
       <c r="C94">
-        <v>-18.14964107889907</v>
+        <v>-18.56841317437051</v>
       </c>
       <c r="D94">
-        <v>10.90035892110093</v>
+        <v>10.8165868256295</v>
       </c>
       <c r="E94">
-        <v>30.82</v>
+        <v>31.155</v>
       </c>
       <c r="F94">
-        <v>30.82</v>
+        <v>31.155</v>
       </c>
       <c r="G94">
         <v>1.77</v>
@@ -8995,37 +8995,37 @@
         <v>2.47</v>
       </c>
       <c r="M94">
-        <v>7.267356</v>
+        <v>7.346349000000001</v>
       </c>
       <c r="N94">
-        <v>-4.797356000000001</v>
+        <v>-4.876349000000001</v>
       </c>
       <c r="O94">
-        <v>-0.7196034000000001</v>
+        <v>-0.7314523500000002</v>
       </c>
       <c r="P94">
-        <v>-4.0777526</v>
+        <v>-4.144896650000001</v>
       </c>
       <c r="Q94">
-        <v>-2.9177526</v>
+        <v>-2.98489665</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7295863731312036</v>
+        <v>0.8272701407213756</v>
       </c>
       <c r="T94">
-        <v>8.912028699957919</v>
+        <v>10.18517565709477</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0509814023146795</v>
+        <v>0.05043321519301627</v>
       </c>
       <c r="W94">
-        <v>0.2237785853341986</v>
+        <v>0.2239078478574868</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3398760154311966</v>
+        <v>0.3362214346201085</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.266143208357959</v>
+        <v>0.268043208357959</v>
       </c>
       <c r="C95">
-        <v>-18.56841317437051</v>
+        <v>-18.9859074693552</v>
       </c>
       <c r="D95">
-        <v>10.8165868256295</v>
+        <v>10.7340925306448</v>
       </c>
       <c r="E95">
-        <v>31.155</v>
+        <v>31.49</v>
       </c>
       <c r="F95">
-        <v>31.155</v>
+        <v>31.49</v>
       </c>
       <c r="G95">
         <v>1.77</v>
@@ -9077,37 +9077,37 @@
         <v>2.47</v>
       </c>
       <c r="M95">
-        <v>7.346349000000001</v>
+        <v>7.425342000000001</v>
       </c>
       <c r="N95">
-        <v>-4.876349000000001</v>
+        <v>-4.955342000000001</v>
       </c>
       <c r="O95">
-        <v>-0.7314523500000002</v>
+        <v>-0.7433013000000001</v>
       </c>
       <c r="P95">
-        <v>-4.144896650000001</v>
+        <v>-4.212040700000001</v>
       </c>
       <c r="Q95">
-        <v>-2.98489665</v>
+        <v>-3.052040700000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8272701407213756</v>
+        <v>0.9575151641749385</v>
       </c>
       <c r="T95">
-        <v>10.18517565709477</v>
+        <v>11.88270493327723</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05043321519301627</v>
+        <v>0.04989669162713312</v>
       </c>
       <c r="W95">
-        <v>0.2239078478574868</v>
+        <v>0.224034360114322</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3362214346201085</v>
+        <v>0.3326446108475541</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.268043208357959</v>
+        <v>0.269943208357959</v>
       </c>
       <c r="C96">
-        <v>-18.9859074693552</v>
+        <v>-19.40215297856984</v>
       </c>
       <c r="D96">
-        <v>10.7340925306448</v>
+        <v>10.65284702143016</v>
       </c>
       <c r="E96">
-        <v>31.49</v>
+        <v>31.825</v>
       </c>
       <c r="F96">
-        <v>31.49</v>
+        <v>31.825</v>
       </c>
       <c r="G96">
         <v>1.77</v>
@@ -9159,37 +9159,37 @@
         <v>2.47</v>
       </c>
       <c r="M96">
-        <v>7.425342000000001</v>
+        <v>7.504335000000001</v>
       </c>
       <c r="N96">
-        <v>-4.955342000000001</v>
+        <v>-5.034335000000001</v>
       </c>
       <c r="O96">
-        <v>-0.7433013000000001</v>
+        <v>-0.7551502500000001</v>
       </c>
       <c r="P96">
-        <v>-4.212040700000001</v>
+        <v>-4.279184750000002</v>
       </c>
       <c r="Q96">
-        <v>-3.052040700000001</v>
+        <v>-3.119184750000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9575151641749385</v>
+        <v>1.139858197009927</v>
       </c>
       <c r="T96">
-        <v>11.88270493327723</v>
+        <v>14.25924591993268</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04989669162713312</v>
+        <v>0.04937146329421593</v>
       </c>
       <c r="W96">
-        <v>0.224034360114322</v>
+        <v>0.2241582089552239</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3326446108475541</v>
+        <v>0.3291430886281063</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.269943208357959</v>
+        <v>0.271843208357959</v>
       </c>
       <c r="C97">
-        <v>-19.40215297856984</v>
+        <v>-19.81717784488951</v>
       </c>
       <c r="D97">
-        <v>10.65284702143016</v>
+        <v>10.57282215511049</v>
       </c>
       <c r="E97">
-        <v>31.825</v>
+        <v>32.16</v>
       </c>
       <c r="F97">
-        <v>31.825</v>
+        <v>32.16</v>
       </c>
       <c r="G97">
         <v>1.77</v>
@@ -9241,37 +9241,37 @@
         <v>2.47</v>
       </c>
       <c r="M97">
-        <v>7.504335000000001</v>
+        <v>7.583328000000002</v>
       </c>
       <c r="N97">
-        <v>-5.034335000000001</v>
+        <v>-5.113328000000002</v>
       </c>
       <c r="O97">
-        <v>-0.7551502500000001</v>
+        <v>-0.7669992000000002</v>
       </c>
       <c r="P97">
-        <v>-4.279184750000002</v>
+        <v>-4.346328800000002</v>
       </c>
       <c r="Q97">
-        <v>-3.119184750000001</v>
+        <v>-3.186328800000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.139858197009927</v>
+        <v>1.413372746262409</v>
       </c>
       <c r="T97">
-        <v>14.25924591993268</v>
+        <v>17.82405739991586</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04937146329421593</v>
+        <v>0.04885717721823452</v>
       </c>
       <c r="W97">
-        <v>0.2241582089552239</v>
+        <v>0.2242794776119403</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3291430886281063</v>
+        <v>0.3257145147882301</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2718432083579589</v>
+        <v>0.273743208357959</v>
       </c>
       <c r="C98">
-        <v>-19.81717784488951</v>
+        <v>-20.23100937185016</v>
       </c>
       <c r="D98">
-        <v>10.57282215511049</v>
+        <v>10.49399062814984</v>
       </c>
       <c r="E98">
-        <v>32.16</v>
+        <v>32.495</v>
       </c>
       <c r="F98">
-        <v>32.16</v>
+        <v>32.495</v>
       </c>
       <c r="G98">
         <v>1.77</v>
@@ -9323,37 +9323,37 @@
         <v>2.47</v>
       </c>
       <c r="M98">
-        <v>7.583328</v>
+        <v>7.662320999999999</v>
       </c>
       <c r="N98">
-        <v>-5.113328</v>
+        <v>-5.192321</v>
       </c>
       <c r="O98">
-        <v>-0.7669992</v>
+        <v>-0.77884815</v>
       </c>
       <c r="P98">
-        <v>-4.3463288</v>
+        <v>-4.41347285</v>
       </c>
       <c r="Q98">
-        <v>-3.1863288</v>
+        <v>-3.25347285</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.413372746262405</v>
+        <v>1.869230328349874</v>
       </c>
       <c r="T98">
-        <v>17.82405739991581</v>
+        <v>23.76540986655442</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04885717721823452</v>
+        <v>0.04835349497887128</v>
       </c>
       <c r="W98">
-        <v>0.2242794776119403</v>
+        <v>0.2243982458839822</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3257145147882301</v>
+        <v>0.3223566331924752</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.273743208357959</v>
+        <v>0.275643208357959</v>
       </c>
       <c r="C99">
-        <v>-20.23100937185016</v>
+        <v>-20.64367405470783</v>
       </c>
       <c r="D99">
-        <v>10.49399062814984</v>
+        <v>10.41632594529217</v>
       </c>
       <c r="E99">
-        <v>32.495</v>
+        <v>32.83</v>
       </c>
       <c r="F99">
-        <v>32.495</v>
+        <v>32.83</v>
       </c>
       <c r="G99">
         <v>1.77</v>
@@ -9405,37 +9405,37 @@
         <v>2.47</v>
       </c>
       <c r="M99">
-        <v>7.662320999999999</v>
+        <v>7.741314</v>
       </c>
       <c r="N99">
-        <v>-5.192321</v>
+        <v>-5.271314</v>
       </c>
       <c r="O99">
-        <v>-0.77884815</v>
+        <v>-0.7906971</v>
       </c>
       <c r="P99">
-        <v>-4.41347285</v>
+        <v>-4.4806169</v>
       </c>
       <c r="Q99">
-        <v>-3.25347285</v>
+        <v>-3.3206169</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.869230328349874</v>
+        <v>2.780945492524811</v>
       </c>
       <c r="T99">
-        <v>23.76540986655442</v>
+        <v>35.64811479983163</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04835349497887128</v>
+        <v>0.0478600919688828</v>
       </c>
       <c r="W99">
-        <v>0.2243982458839822</v>
+        <v>0.2245145903137375</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3223566331924752</v>
+        <v>0.319067279792552</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.275643208357959</v>
+        <v>0.2775432083579589</v>
       </c>
       <c r="C100">
-        <v>-20.64367405470783</v>
+        <v>-21.0551976101288</v>
       </c>
       <c r="D100">
-        <v>10.41632594529217</v>
+        <v>10.3398023898712</v>
       </c>
       <c r="E100">
-        <v>32.83</v>
+        <v>33.165</v>
       </c>
       <c r="F100">
-        <v>32.83</v>
+        <v>33.165</v>
       </c>
       <c r="G100">
         <v>1.77</v>
@@ -9487,37 +9487,37 @@
         <v>2.47</v>
       </c>
       <c r="M100">
-        <v>7.741314</v>
+        <v>7.820307</v>
       </c>
       <c r="N100">
-        <v>-5.271314</v>
+        <v>-5.350307</v>
       </c>
       <c r="O100">
-        <v>-0.7906971</v>
+        <v>-0.80254605</v>
       </c>
       <c r="P100">
-        <v>-4.4806169</v>
+        <v>-4.54776095</v>
       </c>
       <c r="Q100">
-        <v>-3.3206169</v>
+        <v>-3.38776095</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.780945492524811</v>
+        <v>5.516090985049621</v>
       </c>
       <c r="T100">
-        <v>35.64811479983163</v>
+        <v>71.29622959966325</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0478600919688828</v>
+        <v>0.04737665669646984</v>
       </c>
       <c r="W100">
-        <v>0.2245145903137375</v>
+        <v>0.2246285843509724</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.319067279792552</v>
+        <v>0.3158443779764656</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2775432083579589</v>
-      </c>
-      <c r="C101">
-        <v>-21.0551976101288</v>
-      </c>
-      <c r="D101">
-        <v>10.3398023898712</v>
-      </c>
-      <c r="E101">
-        <v>33.165</v>
-      </c>
-      <c r="F101">
-        <v>33.165</v>
-      </c>
-      <c r="G101">
-        <v>1.77</v>
-      </c>
-      <c r="H101">
-        <v>33.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.63</v>
-      </c>
-      <c r="K101">
-        <v>1.16</v>
-      </c>
-      <c r="L101">
-        <v>2.47</v>
-      </c>
-      <c r="M101">
-        <v>7.820307</v>
-      </c>
-      <c r="N101">
-        <v>-5.350307</v>
-      </c>
-      <c r="O101">
-        <v>-0.80254605</v>
-      </c>
-      <c r="P101">
-        <v>-4.54776095</v>
-      </c>
-      <c r="Q101">
-        <v>-3.38776095</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.516090985049621</v>
-      </c>
-      <c r="T101">
-        <v>71.29622959966325</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04737665669646984</v>
-      </c>
-      <c r="W101">
-        <v>0.2246285843509724</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3158443779764656</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
